--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9oct26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9oct26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB46F37-1C9B-4E30-80D8-605F810A27F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B7605E-1166-4A55-B025-B71DDBAA31E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -22325,6 +22325,7 @@
       <c r="I978" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9oct26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_9oct26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4899F22E-6A05-40E3-8F58-8C65FE3607CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B22D18-31BA-4BFA-9779-6BC63EE17DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1202,7 +1202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1380,19 +1380,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1759,131 +1753,117 @@
         <v>238</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3">
-        <v>46281.416666666664</v>
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>706</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-37.742504410000002</v>
+        <v>20.58191759</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5">
-        <v>1134</v>
+        <v>2048.4</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="L2" s="18">
-        <v>17940</v>
-      </c>
-      <c r="M2" s="18">
-        <f>ABS((D2*E2)-L2)</f>
-        <v>10880</v>
-      </c>
-      <c r="N2" s="10" t="str">
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B2, $C$2:$C$681, C2, $D$2:$D$681, D2, $E$2:$E$681, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
-        <v>46281.416666666664</v>
+      <c r="P2" s="24"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
-        <v>726</v>
+        <v>2435</v>
       </c>
       <c r="F3" s="4">
-        <v>-35.978835979999999</v>
+        <v>18.873266940000001</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>282</v>
+        <v>71</v>
       </c>
       <c r="H3" s="5">
-        <v>1134</v>
+        <v>2048.4</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="L3" s="18">
-        <v>17940</v>
-      </c>
-      <c r="M3" s="18">
-        <f>ABS((D3*E3)-L3)</f>
-        <v>10680</v>
-      </c>
-      <c r="N3" s="10" t="str">
+      <c r="J3" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B3, $C$2:$C$681, C3, $D$2:$D$681, D3, $E$2:$E$681, E3) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>61</v>
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>46252.645138888889</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4">
-        <v>660</v>
+        <v>401</v>
       </c>
       <c r="F4" s="4">
-        <v>-23.166472639999999</v>
+        <v>8.3930260850000007</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="H4" s="5">
-        <v>859</v>
+        <v>369.95</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="59" t="s">
         <v>40</v>
       </c>
       <c r="K4" s="17"/>
@@ -1893,75 +1873,88 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B4, $C$2:$C$681, C4, $D$2:$D$681, D4, $E$2:$E$681, E4) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
-        <v>61</v>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4">
-        <v>2560</v>
+        <v>204</v>
       </c>
       <c r="F5" s="4">
-        <v>-22.914784699999998</v>
+        <v>7.4249605059999997</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="H5" s="5">
-        <v>3321</v>
+        <v>189.9</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" t="str">
+      <c r="K5" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="L5" s="18">
+        <v>10550</v>
+      </c>
+      <c r="M5" s="18">
+        <f>ABS((D5*E5)-L5)</f>
+        <v>350</v>
+      </c>
+      <c r="N5" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B5, $C$2:$C$681, C5, $D$2:$D$681, D5, $E$2:$E$681, E5) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E6" s="4">
-        <v>2660</v>
+        <v>201</v>
       </c>
       <c r="F6" s="4">
-        <v>-19.903643479999999</v>
+        <v>5.8451816750000001</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5">
-        <v>3321</v>
+        <v>189.9</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="35"/>
+      <c r="J6" s="36" t="s">
+        <v>40</v>
+      </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
@@ -1970,74 +1963,85 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>61</v>
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>46275.457638888889</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4">
-        <v>2752</v>
+        <v>222</v>
       </c>
       <c r="F7" s="4">
-        <v>-17.133393559999998</v>
+        <v>5.8150619639999999</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="H7" s="5">
-        <v>3321</v>
+        <v>209.8</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="35" t="s">
+      <c r="J7" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" t="str">
+      <c r="K7" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="L7" s="18">
+        <v>56375</v>
+      </c>
+      <c r="M7" s="18">
+        <f>ABS((D7*E7)-L7)</f>
+        <v>34175</v>
+      </c>
+      <c r="N7" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B7, $C$2:$C$681, C7, $D$2:$D$681, D7, $E$2:$E$681, E7) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4">
-        <v>4014</v>
+        <v>1614</v>
       </c>
       <c r="F8" s="4">
-        <v>-15.01344456</v>
+        <v>5.4901960780000003</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H8" s="5">
-        <v>4723.1000000000004</v>
+        <v>1530</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="35"/>
+      <c r="J8" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
@@ -2046,37 +2050,35 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="9" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
-        <v>46252.688194444447</v>
+    <row r="9" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4">
-        <v>136.15</v>
+        <v>3888</v>
       </c>
       <c r="F9" s="4">
-        <v>-14.895611949999999</v>
+        <v>5.1948051949999998</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="H9" s="5">
-        <v>159.97999999999999</v>
+        <v>3696</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="35" t="s">
-        <v>54</v>
-      </c>
+      <c r="J9" s="35"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
@@ -2084,109 +2086,95 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B9, $C$2:$C$681, C9, $D$2:$D$681, D9, $E$2:$E$681, E9) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="48">
-        <v>46289.375</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="O9" s="25"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5">
-        <v>5</v>
-      </c>
-      <c r="E10" s="5">
-        <v>601</v>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3856</v>
       </c>
       <c r="F10" s="4">
-        <v>-14.87252125</v>
+        <v>4.329004329</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="H10" s="5">
-        <v>706</v>
+        <v>3696</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="35"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$681, B10, $C$2:$C$681, C10, $D$2:$D$681, D10, $E$2:$E$681, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O10" s="19"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>4010</v>
+      </c>
+      <c r="F11" s="4">
+        <v>3.7033205749999998</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3866.8</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="L10" s="18">
-        <v>3245</v>
-      </c>
-      <c r="M10" s="18">
-        <f>ABS((D10*E10)-L10)</f>
-        <v>240</v>
-      </c>
-      <c r="N10" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B10, $C$2:$C$681, C10, $D$2:$D$681, D10, $E$2:$E$681, E10) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="48">
-        <v>46303.375</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1294</v>
-      </c>
-      <c r="F11" s="4">
-        <v>-13.629688959999999</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1498.2</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="L11" s="18">
-        <v>2852</v>
-      </c>
-      <c r="M11" s="18">
-        <f>ABS((D11*E11)-L11)</f>
-        <v>264</v>
-      </c>
-      <c r="N11" s="10" t="str">
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B11, $C$2:$C$681, C11, $D$2:$D$681, D11, $E$2:$E$681, E11) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
-        <v>46252.635416666664</v>
+    <row r="12" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
@@ -2195,16 +2183,16 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>2892</v>
+        <v>3830</v>
       </c>
       <c r="F12" s="4">
-        <v>-12.91779584</v>
+        <v>3.6255411259999999</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H12" s="5">
-        <v>3321</v>
+        <v>3696</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
@@ -2217,77 +2205,74 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B12, $C$2:$C$681, C12, $D$2:$D$681, D12, $E$2:$E$681, E12) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="48">
-        <v>46295.375</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+    </row>
+    <row r="13" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>46252.635416666664</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="5">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5">
-        <v>620</v>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1302</v>
       </c>
       <c r="F13" s="4">
-        <v>-12.181303120000001</v>
+        <v>3.4976152620000001</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H13" s="5">
-        <v>706</v>
+        <v>1258</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="L13" s="18">
-        <v>3395</v>
-      </c>
-      <c r="M13" s="18">
-        <f>ABS((D13*E13)-L13)</f>
-        <v>295</v>
-      </c>
-      <c r="N13" s="10" t="str">
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B13, $C$2:$C$681, C13, $D$2:$D$681, D13, $E$2:$E$681, E13) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O13"/>
+      <c r="P13"/>
+    </row>
+    <row r="14" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4">
-        <v>4164</v>
+        <v>3810</v>
       </c>
       <c r="F14" s="4">
-        <v>-11.837564309999999</v>
+        <v>3.0844155839999998</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="H14" s="5">
-        <v>4723.1000000000004</v>
+        <v>3696</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
@@ -2300,39 +2285,37 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B14, $C$2:$C$681, C14, $D$2:$D$681, D14, $E$2:$E$681, E14) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O14"/>
-      <c r="P14"/>
-    </row>
-    <row r="15" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4">
-        <v>251</v>
+        <v>6920</v>
       </c>
       <c r="F15" s="4">
-        <v>-11.61971831</v>
+        <v>2.2307578669999999</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H15" s="5">
-        <v>284</v>
+        <v>6769</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="35" t="s">
-        <v>40</v>
+      <c r="J15" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -2344,76 +2327,83 @@
       <c r="O15"/>
       <c r="P15"/>
     </row>
-    <row r="16" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
-        <v>61</v>
+    <row r="16" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="4">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="E16" s="4">
-        <v>701</v>
+        <v>214</v>
       </c>
       <c r="F16" s="4">
-        <v>-10.495403469999999</v>
+        <v>2.0019065779999998</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="H16" s="5">
-        <v>783.2</v>
+        <v>209.8</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" t="str">
+      <c r="J16" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="L16" s="18">
+        <v>21900</v>
+      </c>
+      <c r="M16" s="18">
+        <f>ABS((D16*E16)-L16)</f>
+        <v>500</v>
+      </c>
+      <c r="N16" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B16, $C$2:$C$681, C16, $D$2:$D$681, D16, $E$2:$E$681, E16) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O16"/>
-      <c r="P16"/>
-    </row>
-    <row r="17" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E17" s="4">
-        <v>111</v>
+        <v>862</v>
       </c>
       <c r="F17" s="4">
-        <v>-9.5943964820000005</v>
+        <v>1.8731903329999999</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="H17" s="5">
-        <v>122.78</v>
+        <v>846.15</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="35"/>
+      <c r="J17" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
@@ -2424,30 +2414,30 @@
       <c r="O17"/>
       <c r="P17"/>
     </row>
-    <row r="18" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>18052</v>
+        <v>3760</v>
       </c>
       <c r="F18" s="4">
-        <v>-9.5137844610000002</v>
+        <v>1.7316017319999999</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="H18" s="5">
-        <v>19950</v>
+        <v>3696</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
@@ -2461,32 +2451,32 @@
         <v>Unique</v>
       </c>
       <c r="O18"/>
-      <c r="P18"/>
-    </row>
-    <row r="19" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="4">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="E19" s="4">
-        <v>1751</v>
+        <v>1277</v>
       </c>
       <c r="F19" s="4">
-        <v>-9.2699103580000006</v>
+        <v>1.5103338630000001</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="H19" s="5">
-        <v>1929.9</v>
+        <v>1258</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
@@ -2502,138 +2492,141 @@
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
-        <v>61</v>
+    <row r="20" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>46283.375</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E20" s="4">
-        <v>4364</v>
+        <v>870.2</v>
       </c>
       <c r="F20" s="4">
-        <v>-7.603057314</v>
+        <v>1.356939025</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5">
-        <v>4723.1000000000004</v>
+        <v>858.55</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" t="str">
+      <c r="J20" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="L20" s="18">
+        <v>17920</v>
+      </c>
+      <c r="M20" s="18">
+        <f>ABS((D20*E20)-L20)</f>
+        <v>516</v>
+      </c>
+      <c r="N20" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B20, $C$2:$C$681, C20, $D$2:$D$681, D20, $E$2:$E$681, E20) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O20"/>
-      <c r="P20"/>
-    </row>
-    <row r="21" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>61</v>
+    </row>
+    <row r="21" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E21" s="4">
-        <v>18552</v>
+        <v>870</v>
       </c>
       <c r="F21" s="4">
-        <v>-7.0075187970000004</v>
+        <v>1.333643935</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H21" s="5">
-        <v>19950</v>
+        <v>858.55</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" t="str">
+      <c r="J21" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="L21" s="18">
+        <v>17700</v>
+      </c>
+      <c r="M21" s="18">
+        <f>ABS((D21*E21)-L21)</f>
+        <v>300</v>
+      </c>
+      <c r="N21" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B21, $C$2:$C$681, C21, $D$2:$D$681, D21, $E$2:$E$681, E21) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O21"/>
-      <c r="P21"/>
-    </row>
-    <row r="22" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3">
-        <v>46121.375</v>
+      <c r="P21" s="24"/>
+    </row>
+    <row r="22" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E22" s="4">
-        <v>1614</v>
+        <v>212</v>
       </c>
       <c r="F22" s="4">
-        <v>-6.9740634010000004</v>
+        <v>1.048617731</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="H22" s="5">
-        <v>1735</v>
+        <v>209.8</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="23" t="s">
+      <c r="J22" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K22" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="L22" s="18">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
-      <c r="M22" s="18">
-        <f>ABS((D22*E22)-L22)</f>
-        <v>540</v>
-      </c>
-      <c r="N22" s="10" t="str">
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B22, $C$2:$C$681, C22, $D$2:$D$681, D22, $E$2:$E$681, E22) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O22"/>
-      <c r="P22"/>
-    </row>
-    <row r="23" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>61</v>
+    </row>
+    <row r="23" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
@@ -2642,13 +2635,13 @@
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="E23" s="4">
-        <v>115.25</v>
+        <v>122</v>
       </c>
       <c r="F23" s="4">
-        <v>-6.1329206709999999</v>
+        <v>-0.63528261929999996</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>85</v>
@@ -2659,7 +2652,9 @@
       <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="35"/>
+      <c r="J23" s="36" t="s">
+        <v>40</v>
+      </c>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
@@ -2667,77 +2662,86 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B23, $C$2:$C$681, C23, $D$2:$D$681, D23, $E$2:$E$681, E23) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O23"/>
-      <c r="P23"/>
-    </row>
-    <row r="24" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
-        <v>61</v>
+    </row>
+    <row r="24" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
+        <v>46258.601388888892</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E24" s="4">
-        <v>116</v>
+        <v>2271</v>
       </c>
       <c r="F24" s="4">
-        <v>-5.5220719989999996</v>
+        <v>-0.95944177929999996</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H24" s="5">
-        <v>122.78</v>
+        <v>2293</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="35"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" t="str">
+      <c r="J24" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="L24" s="18">
+        <v>7113</v>
+      </c>
+      <c r="M24" s="18">
+        <f>ABS((D24*E24)-L24)</f>
+        <v>300</v>
+      </c>
+      <c r="N24" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B24, $C$2:$C$681, C24, $D$2:$D$681, D24, $E$2:$E$681, E24) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
-        <v>61</v>
+    <row r="25" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E25" s="4">
-        <v>4415</v>
+        <v>850</v>
       </c>
       <c r="F25" s="4">
-        <v>-5.3590568059999999</v>
+        <v>-0.99586512140000005</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="H25" s="5">
-        <v>4665</v>
+        <v>858.55</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="35"/>
+      <c r="J25" s="36" t="s">
+        <v>54</v>
+      </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
@@ -2745,80 +2749,78 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B25, $C$2:$C$681, C25, $D$2:$D$681, D25, $E$2:$E$681, E25) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3">
-        <v>46302.468055555553</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="1" t="s">
+    <row r="26" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48">
+        <v>46304.375416666669</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="4">
-        <v>2</v>
-      </c>
-      <c r="E26" s="4">
-        <v>3110</v>
+      <c r="D26" s="5">
+        <v>10</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1708.7</v>
       </c>
       <c r="F26" s="4">
-        <v>-5.3272450530000004</v>
+        <v>-1.5158501440000001</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H26" s="5">
-        <v>3285</v>
+        <v>1735</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="L26" s="18">
-        <f>2*3334</f>
-        <v>6668</v>
+        <v>17487</v>
       </c>
       <c r="M26" s="18">
         <f>ABS((D26*E26)-L26)</f>
-        <v>448</v>
-      </c>
-      <c r="N26" s="10" t="str">
+        <v>400</v>
+      </c>
+      <c r="N26" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B26, $C$2:$C$681, C26, $D$2:$D$681, D26, $E$2:$E$681, E26) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="48">
-        <v>46304.38784722222</v>
+        <v>46304.375416666669</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="5">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E27" s="5">
-        <v>30.3</v>
+        <v>832</v>
       </c>
       <c r="F27" s="4">
-        <v>-4.896421846</v>
+        <v>-1.6722803289999999</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H27" s="5">
-        <v>31.86</v>
+        <v>846.15</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
@@ -2827,131 +2829,132 @@
         <v>54</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="L27" s="18">
-        <v>15850</v>
+        <v>8570</v>
       </c>
       <c r="M27" s="18">
         <f>ABS((D27*E27)-L27)</f>
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="N27" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B27, $C$2:$C$681, C27, $D$2:$D$681, D27, $E$2:$E$681, E27) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="28" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48">
-        <v>46300.375694444447</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    <row r="28" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5">
-        <v>4510</v>
+      <c r="D28" s="4">
+        <v>50</v>
+      </c>
+      <c r="E28" s="4">
+        <v>206</v>
       </c>
       <c r="F28" s="4">
-        <v>-4.5118672059999998</v>
+        <v>-1.811248808</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="H28" s="5">
-        <v>4723.1000000000004</v>
+        <v>209.8</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="L28" s="18">
-        <v>4763</v>
-      </c>
-      <c r="M28" s="18">
-        <f>ABS((D28*E28)-L28)</f>
-        <v>253</v>
-      </c>
-      <c r="N28" s="10" t="str">
+      <c r="J28" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B28, $C$2:$C$681, C28, $D$2:$D$681, D28, $E$2:$E$681, E28) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-    </row>
-    <row r="29" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="6" t="s">
-        <v>61</v>
+      <c r="O28"/>
+      <c r="P28"/>
+    </row>
+    <row r="29" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="3">
+        <v>46286.375</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" s="4">
-        <v>4456</v>
+        <v>702</v>
       </c>
       <c r="F29" s="4">
-        <v>-4.48017149</v>
+        <v>-1.8319116209999999</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="H29" s="5">
-        <v>4665</v>
+        <v>715.1</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="35"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" t="str">
+      <c r="J29" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="L29" s="18">
+        <f>7470/2</f>
+        <v>3735</v>
+      </c>
+      <c r="M29" s="18">
+        <f>ABS((D29*E29)-L29)</f>
+        <v>225</v>
+      </c>
+      <c r="N29" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B29, $C$2:$C$681, C29, $D$2:$D$681, D29, $E$2:$E$681, E29) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O29"/>
-      <c r="P29"/>
-    </row>
-    <row r="30" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="48">
-        <v>46301.375694444447</v>
+        <v>46301.393055555556</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5">
-        <v>1664</v>
+        <v>19550</v>
       </c>
       <c r="F30" s="4">
-        <v>-4.0922190199999999</v>
+        <v>-2.0050125310000002</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H30" s="5">
-        <v>1735</v>
+        <v>19950</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
@@ -2960,91 +2963,90 @@
         <v>40</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L30" s="18">
-        <f>5*1752</f>
-        <v>8760</v>
+        <v>20020</v>
       </c>
       <c r="M30" s="18">
         <f>ABS((D30*E30)-L30)</f>
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="N30" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B30, $C$2:$C$681, C30, $D$2:$D$681, D30, $E$2:$E$681, E30) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3">
-        <v>46031.4375</v>
+    <row r="31" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="4">
-        <v>1052</v>
+        <v>4560</v>
       </c>
       <c r="F31" s="4">
-        <v>-3.3088235290000001</v>
+        <v>-2.2508038589999999</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="H31" s="5">
-        <v>1088</v>
+        <v>4665</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="M31" s="18">
-        <f>ABS((D31*E31)-L31)</f>
-        <v>3156</v>
-      </c>
-      <c r="N31" s="10" t="str">
+      <c r="J31" s="35"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B31, $C$2:$C$681, C31, $D$2:$D$681, D31, $E$2:$E$681, E31) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P31" s="19"/>
-    </row>
-    <row r="32" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O31"/>
+      <c r="P31"/>
+    </row>
+    <row r="32" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E32" s="4">
-        <v>119</v>
+        <v>836</v>
       </c>
       <c r="F32" s="4">
-        <v>-3.0786773090000001</v>
+        <v>-2.6265214609999998</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32" s="5">
-        <v>122.78</v>
+        <v>858.55</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="35"/>
+      <c r="J32" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="K32" s="17"/>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
@@ -3053,54 +3055,50 @@
         <v>Unique</v>
       </c>
       <c r="O32"/>
-    </row>
-    <row r="33" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48">
-        <v>46304.388981481483</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="P32"/>
+    </row>
+    <row r="33" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
+        <v>46252.6875</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="5">
-        <v>9</v>
-      </c>
-      <c r="E33" s="5">
-        <v>2105</v>
+      <c r="D33" s="4">
+        <v>25</v>
+      </c>
+      <c r="E33" s="4">
+        <v>326</v>
       </c>
       <c r="F33" s="4">
-        <v>-3.0623992630000001</v>
+        <v>-2.686567164</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="H33" s="5">
-        <v>2171.5</v>
+        <v>335</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="L33" s="18">
-        <v>19395</v>
-      </c>
-      <c r="M33" s="18">
-        <f>ABS((D33*E33)-L33)</f>
-        <v>450</v>
-      </c>
+      <c r="J33" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
       <c r="N33" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B33, $C$2:$C$681, C33, $D$2:$D$681, D33, $E$2:$E$681, E33) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O33"/>
+      <c r="P33"/>
+    </row>
+    <row r="34" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <v>46254.375</v>
       </c>
@@ -3143,78 +3141,81 @@
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="3">
-        <v>46252.6875</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="1" t="s">
+    <row r="35" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48">
+        <v>46304.388981481483</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="4">
-        <v>25</v>
-      </c>
-      <c r="E35" s="4">
-        <v>326</v>
+      <c r="D35" s="5">
+        <v>9</v>
+      </c>
+      <c r="E35" s="5">
+        <v>2105</v>
       </c>
       <c r="F35" s="4">
-        <v>-2.686567164</v>
+        <v>-3.0623992630000001</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="H35" s="5">
-        <v>335</v>
+        <v>2171.5</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="J35" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="L35" s="18">
+        <v>19395</v>
+      </c>
+      <c r="M35" s="18">
+        <f>ABS((D35*E35)-L35)</f>
+        <v>450</v>
+      </c>
       <c r="N35" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B35, $C$2:$C$681, C35, $D$2:$D$681, D35, $E$2:$E$681, E35) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O35"/>
-      <c r="P35"/>
-    </row>
-    <row r="36" spans="1:16" s="24" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:16" s="24" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E36" s="4">
-        <v>836</v>
+        <v>119</v>
       </c>
       <c r="F36" s="4">
-        <v>-2.6265214609999998</v>
+        <v>-3.0786773090000001</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36" s="5">
-        <v>858.55</v>
+        <v>122.78</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="35" t="s">
-        <v>40</v>
-      </c>
+      <c r="J36" s="35"/>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
@@ -3223,71 +3224,76 @@
         <v>Unique</v>
       </c>
       <c r="O36"/>
-      <c r="P36"/>
-    </row>
-    <row r="37" spans="1:16" s="29" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
-        <v>61</v>
+      <c r="P36" s="10"/>
+    </row>
+    <row r="37" spans="1:16" s="29" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
+        <v>46031.4375</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="4">
-        <v>4560</v>
+        <v>1052</v>
       </c>
       <c r="F37" s="4">
-        <v>-2.2508038589999999</v>
+        <v>-3.3088235290000001</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="H37" s="5">
-        <v>4665</v>
+        <v>1088</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="35"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" t="str">
+      <c r="J37" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18">
+        <f>ABS((D37*E37)-L37)</f>
+        <v>3156</v>
+      </c>
+      <c r="N37" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B37, $C$2:$C$681, C37, $D$2:$D$681, D37, $E$2:$E$681, E37) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O37"/>
-      <c r="P37"/>
-    </row>
-    <row r="38" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O37" s="10"/>
+      <c r="P37" s="19"/>
+    </row>
+    <row r="38" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="48">
-        <v>46301.393055555556</v>
+        <v>46301.375694444447</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5">
-        <v>19550</v>
+        <v>1664</v>
       </c>
       <c r="F38" s="4">
-        <v>-2.0050125310000002</v>
+        <v>-4.0922190199999999</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H38" s="5">
-        <v>19950</v>
+        <v>1735</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
@@ -3296,148 +3302,146 @@
         <v>40</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L38" s="18">
-        <v>20020</v>
+        <f>5*1752</f>
+        <v>8760</v>
       </c>
       <c r="M38" s="18">
         <f>ABS((D38*E38)-L38)</f>
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="N38" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B38, $C$2:$C$681, C38, $D$2:$D$681, D38, $E$2:$E$681, E38) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="3">
-        <v>46286.375</v>
+    <row r="39" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E39" s="4">
-        <v>702</v>
+        <v>4456</v>
       </c>
       <c r="F39" s="4">
-        <v>-1.8319116209999999</v>
+        <v>-4.48017149</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="H39" s="5">
-        <v>715.1</v>
+        <v>4665</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="L39" s="18">
-        <f>7470/2</f>
-        <v>3735</v>
-      </c>
-      <c r="M39" s="18">
-        <f>ABS((D39*E39)-L39)</f>
-        <v>225</v>
-      </c>
-      <c r="N39" s="10" t="str">
+      <c r="J39" s="35"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B39, $C$2:$C$681, C39, $D$2:$D$681, D39, $E$2:$E$681, E39) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="O39"/>
+      <c r="P39"/>
+    </row>
+    <row r="40" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="48">
+        <v>46300.375694444447</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="4">
-        <v>50</v>
-      </c>
-      <c r="E40" s="4">
-        <v>206</v>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5">
+        <v>4510</v>
       </c>
       <c r="F40" s="4">
-        <v>-1.811248808</v>
+        <v>-4.5118672059999998</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="H40" s="5">
-        <v>209.8</v>
+        <v>4723.1000000000004</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" t="str">
+      <c r="J40" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="L40" s="18">
+        <v>4763</v>
+      </c>
+      <c r="M40" s="18">
+        <f>ABS((D40*E40)-L40)</f>
+        <v>253</v>
+      </c>
+      <c r="N40" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B40, $C$2:$C$681, C40, $D$2:$D$681, D40, $E$2:$E$681, E40) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O40"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="48">
-        <v>46304.375416666669</v>
+        <v>46304.38784722222</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="5">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="E41" s="5">
-        <v>832</v>
+        <v>30.3</v>
       </c>
       <c r="F41" s="4">
-        <v>-1.6722803289999999</v>
+        <v>-4.896421846</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H41" s="5">
-        <v>846.15</v>
+        <v>31.86</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="18" t="s">
+      <c r="J41" s="61" t="s">
         <v>54</v>
       </c>
       <c r="K41" s="18" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L41" s="18">
-        <v>8570</v>
+        <v>15850</v>
       </c>
       <c r="M41" s="18">
         <f>ABS((D41*E41)-L41)</f>
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="N41" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B41, $C$2:$C$681, C41, $D$2:$D$681, D41, $E$2:$E$681, E41) &gt; 1, "Duplicate", "Unique")</f>
@@ -3446,85 +3450,84 @@
       <c r="O41" s="10"/>
       <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="48">
-        <v>46304.375416666669</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="2" t="s">
+    <row r="42" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="3">
+        <v>46302.468055555553</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="5">
-        <v>10</v>
-      </c>
-      <c r="E42" s="5">
-        <v>1708.7</v>
+      <c r="D42" s="4">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
+        <v>3110</v>
       </c>
       <c r="F42" s="4">
-        <v>-1.5158501440000001</v>
+        <v>-5.3272450530000004</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H42" s="5">
-        <v>1735</v>
+        <v>3285</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J42" s="18" t="s">
-        <v>54</v>
+      <c r="J42" s="61" t="s">
+        <v>40</v>
       </c>
       <c r="K42" s="18" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="L42" s="18">
-        <v>17487</v>
+        <f>2*3334</f>
+        <v>6668</v>
       </c>
       <c r="M42" s="18">
         <f>ABS((D42*E42)-L42)</f>
-        <v>400</v>
-      </c>
-      <c r="N42" t="str">
+        <v>448</v>
+      </c>
+      <c r="N42" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B42, $C$2:$C$681, C42, $D$2:$D$681, D42, $E$2:$E$681, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="3">
-        <v>46252.635416666664</v>
+    <row r="43" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E43" s="4">
-        <v>850</v>
+        <v>4415</v>
       </c>
       <c r="F43" s="4">
-        <v>-0.99586512140000005</v>
+        <v>-5.3590568059999999</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H43" s="5">
-        <v>858.55</v>
+        <v>4665</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="64" t="s">
-        <v>54</v>
-      </c>
+      <c r="J43" s="62"/>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
@@ -3532,57 +3535,47 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B43, $C$2:$C$681, C43, $D$2:$D$681, D43, $E$2:$E$681, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O43" s="10"/>
-    </row>
-    <row r="44" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="3">
-        <v>46258.601388888892</v>
+    </row>
+    <row r="44" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E44" s="4">
-        <v>2271</v>
+        <v>116</v>
       </c>
       <c r="F44" s="4">
-        <v>-0.95944177929999996</v>
+        <v>-5.5220719989999996</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H44" s="5">
-        <v>2293</v>
+        <v>122.78</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="L44" s="18">
-        <v>7113</v>
-      </c>
-      <c r="M44" s="18">
-        <f>ABS((D44*E44)-L44)</f>
-        <v>300</v>
-      </c>
-      <c r="N44" s="10" t="str">
+      <c r="J44" s="62"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B44, $C$2:$C$681, C44, $D$2:$D$681, D44, $E$2:$E$681, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="45" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="3">
-        <v>46252.6875</v>
+    <row r="45" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>20</v>
@@ -3591,13 +3584,13 @@
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E45" s="4">
-        <v>122</v>
+        <v>115.25</v>
       </c>
       <c r="F45" s="4">
-        <v>-0.63528261929999996</v>
+        <v>-6.1329206709999999</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>85</v>
@@ -3608,9 +3601,7 @@
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="64" t="s">
-        <v>40</v>
-      </c>
+      <c r="J45" s="62"/>
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
@@ -3618,33 +3609,31 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B45, $C$2:$C$681, C45, $D$2:$D$681, D45, $E$2:$E$681, E45) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-    </row>
-    <row r="46" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="6" t="s">
-        <v>61</v>
+    </row>
+    <row r="46" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="3">
+        <v>46121.375</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E46" s="4">
-        <v>212</v>
+        <v>1614</v>
       </c>
       <c r="F46" s="4">
-        <v>1.048617731</v>
+        <v>-6.9740634010000004</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H46" s="5">
-        <v>209.8</v>
+        <v>1735</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
@@ -3652,139 +3641,131 @@
       <c r="J46" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" t="str">
+      <c r="K46" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="L46" s="18">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M46" s="18">
+        <f>ABS((D46*E46)-L46)</f>
+        <v>540</v>
+      </c>
+      <c r="N46" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B46, $C$2:$C$681, C46, $D$2:$D$681, D46, $E$2:$E$681, E46) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-    </row>
-    <row r="47" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="3">
-        <v>46261.375</v>
+    </row>
+    <row r="47" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>870</v>
+        <v>18552</v>
       </c>
       <c r="F47" s="4">
-        <v>1.333643935</v>
+        <v>-7.0075187970000004</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H47" s="5">
-        <v>858.55</v>
+        <v>19950</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="K47" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="L47" s="18">
-        <v>17700</v>
-      </c>
-      <c r="M47" s="18">
-        <f>ABS((D47*E47)-L47)</f>
-        <v>300</v>
-      </c>
-      <c r="N47" s="10" t="str">
+      <c r="J47" s="62"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B47, $C$2:$C$681, C47, $D$2:$D$681, D47, $E$2:$E$681, E47) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O47" s="10"/>
-      <c r="P47" s="24"/>
-    </row>
-    <row r="48" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="3">
-        <v>46283.375</v>
+      <c r="O47"/>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E48" s="4">
-        <v>870.2</v>
+        <v>4364</v>
       </c>
       <c r="F48" s="4">
-        <v>1.356939025</v>
+        <v>-7.603057314</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H48" s="5">
-        <v>858.55</v>
+        <v>4723.1000000000004</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="K48" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="L48" s="18">
-        <v>17920</v>
-      </c>
-      <c r="M48" s="18">
-        <f>ABS((D48*E48)-L48)</f>
-        <v>516</v>
-      </c>
-      <c r="N48" s="10" t="str">
+      <c r="J48" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B48, $C$2:$C$681, C48, $D$2:$D$681, D48, $E$2:$E$681, E48) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O48"/>
+      <c r="P48"/>
+    </row>
+    <row r="49" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="4">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="E49" s="4">
-        <v>1277</v>
+        <v>1751</v>
       </c>
       <c r="F49" s="4">
-        <v>1.5103338630000001</v>
+        <v>-9.2699103580000006</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="H49" s="5">
-        <v>1258</v>
+        <v>1929.9</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="61"/>
+      <c r="J49" s="62"/>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
@@ -3795,35 +3776,35 @@
       <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="4">
-        <v>3760</v>
+        <v>18052</v>
       </c>
       <c r="F50" s="4">
-        <v>1.7316017319999999</v>
+        <v>-9.5137844610000002</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H50" s="5">
-        <v>3696</v>
+        <v>19950</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="61"/>
+      <c r="J50" s="62"/>
       <c r="K50" s="17"/>
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
@@ -3832,8 +3813,9 @@
         <v>Unique</v>
       </c>
       <c r="O50"/>
-    </row>
-    <row r="51" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50"/>
+    </row>
+    <row r="51" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
         <v>46261.375</v>
       </c>
@@ -3880,37 +3862,35 @@
       </c>
       <c r="O51"/>
     </row>
-    <row r="52" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E52" s="4">
-        <v>862</v>
+        <v>111</v>
       </c>
       <c r="F52" s="4">
-        <v>1.8731903329999999</v>
+        <v>-9.5943964820000005</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="H52" s="5">
-        <v>846.15</v>
+        <v>122.78</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="61" t="s">
-        <v>54</v>
-      </c>
+      <c r="J52" s="62"/>
       <c r="K52" s="17"/>
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
@@ -3921,7 +3901,7 @@
       <c r="O52"/>
       <c r="P52"/>
     </row>
-    <row r="53" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="55">
         <v>46290.385416666664</v>
       </c>
@@ -3971,84 +3951,77 @@
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3">
-        <v>46268.385416666664</v>
+    <row r="54" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="4">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E54" s="4">
-        <v>214</v>
+        <v>701</v>
       </c>
       <c r="F54" s="4">
-        <v>2.0019065779999998</v>
+        <v>-10.495403469999999</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="H54" s="5">
-        <v>209.8</v>
+        <v>783.2</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J54" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="K54" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="L54" s="18">
-        <v>21900</v>
-      </c>
-      <c r="M54" s="18">
-        <f>ABS((D54*E54)-L54)</f>
-        <v>500</v>
-      </c>
-      <c r="N54" s="10" t="str">
+        <v>40</v>
+      </c>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B54, $C$2:$C$681, C54, $D$2:$D$681, D54, $E$2:$E$681, E54) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-    </row>
-    <row r="55" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E55" s="4">
-        <v>6920</v>
+        <v>251</v>
       </c>
       <c r="F55" s="4">
-        <v>2.2307578669999999</v>
+        <v>-11.61971831</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H55" s="5">
-        <v>6769</v>
+        <v>284</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="63" t="s">
-        <v>54</v>
+      <c r="J55" s="62" t="s">
+        <v>40</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
@@ -4060,7 +4033,7 @@
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -4074,7 +4047,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="8">
-        <v>2998</v>
+        <v>3040</v>
       </c>
       <c r="F56" s="4">
         <v>2.6360835329999999</v>
@@ -4096,7 +4069,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>46288.429861111108</v>
       </c>
@@ -4142,7 +4115,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="48">
         <v>46304.375462962962</v>
       </c>
@@ -4190,35 +4163,35 @@
       <c r="O58" s="10"/>
       <c r="P58" s="10"/>
     </row>
-    <row r="59" spans="1:16" s="24" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" s="24" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>3810</v>
+        <v>4164</v>
       </c>
       <c r="F59" s="4">
-        <v>3.0844155839999998</v>
+        <v>-11.837564309999999</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="H59" s="5">
-        <v>3696</v>
+        <v>4723.1000000000004</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="61"/>
+      <c r="J59" s="62"/>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
@@ -4226,10 +4199,10 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B59, $C$2:$C$681, C59, $D$2:$D$681, D59, $E$2:$E$681, E59) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-    </row>
-    <row r="60" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O59"/>
+      <c r="P59"/>
+    </row>
+    <row r="60" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="48">
         <v>46296.410416666666</v>
       </c>
@@ -4275,30 +4248,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3">
-        <v>46252.635416666664</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" s="1" t="s">
+    <row r="61" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="48">
+        <v>46295.375</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="4">
-        <v>3</v>
-      </c>
-      <c r="E61" s="4">
-        <v>1302</v>
+      <c r="D61" s="5">
+        <v>5</v>
+      </c>
+      <c r="E61" s="5">
+        <v>620</v>
       </c>
       <c r="F61" s="4">
-        <v>3.4976152620000001</v>
+        <v>-12.181303120000001</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H61" s="5">
-        <v>1258</v>
+        <v>706</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
@@ -4306,22 +4279,27 @@
       <c r="J61" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" t="str">
+      <c r="K61" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="L61" s="18">
+        <v>3395</v>
+      </c>
+      <c r="M61" s="18">
+        <f>ABS((D61*E61)-L61)</f>
+        <v>295</v>
+      </c>
+      <c r="N61" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B61, $C$2:$C$681, C61, $D$2:$D$681, D61, $E$2:$E$681, E61) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O61"/>
-      <c r="P61"/>
-    </row>
-    <row r="62" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="6" t="s">
-        <v>61</v>
+    </row>
+    <row r="62" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
@@ -4330,21 +4308,21 @@
         <v>2</v>
       </c>
       <c r="E62" s="4">
-        <v>3830</v>
+        <v>2892</v>
       </c>
       <c r="F62" s="4">
-        <v>3.6255411259999999</v>
+        <v>-12.91779584</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="H62" s="5">
-        <v>3696</v>
+        <v>3321</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="61"/>
+      <c r="J62" s="62"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
@@ -4352,31 +4330,33 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B62, $C$2:$C$681, C62, $D$2:$D$681, D62, $E$2:$E$681, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" s="24" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="O62"/>
+      <c r="P62"/>
+    </row>
+    <row r="63" spans="1:16" s="24" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="48">
+        <v>46303.375</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="4">
-        <v>1</v>
-      </c>
-      <c r="E63" s="4">
-        <v>4010</v>
+      <c r="D63" s="5">
+        <v>2</v>
+      </c>
+      <c r="E63" s="5">
+        <v>1294</v>
       </c>
       <c r="F63" s="4">
-        <v>3.7033205749999998</v>
+        <v>-13.629688959999999</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="H63" s="5">
-        <v>3866.8</v>
+        <v>1498.2</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
@@ -4384,17 +4364,24 @@
       <c r="J63" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" t="str">
+      <c r="K63" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="L63" s="18">
+        <v>2852</v>
+      </c>
+      <c r="M63" s="18">
+        <f>ABS((D63*E63)-L63)</f>
+        <v>264</v>
+      </c>
+      <c r="N63" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B63, $C$2:$C$681, C63, $D$2:$D$681, D63, $E$2:$E$681, E63) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O63" s="10"/>
       <c r="P63" s="10"/>
     </row>
-    <row r="64" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="3">
         <v>46287.375</v>
       </c>
@@ -4440,7 +4427,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="48">
         <v>46303.375</v>
       </c>
@@ -4486,73 +4473,83 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" s="1" t="s">
+    <row r="66" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="48">
+        <v>46289.375</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="4">
-        <v>2</v>
-      </c>
-      <c r="E66" s="4">
-        <v>3856</v>
+      <c r="D66" s="5">
+        <v>5</v>
+      </c>
+      <c r="E66" s="5">
+        <v>601</v>
       </c>
       <c r="F66" s="4">
-        <v>4.329004329</v>
+        <v>-14.87252125</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="H66" s="5">
-        <v>3696</v>
+        <v>706</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="61"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" t="str">
+      <c r="J66" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="K66" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="L66" s="18">
+        <v>3245</v>
+      </c>
+      <c r="M66" s="18">
+        <f>ABS((D66*E66)-L66)</f>
+        <v>240</v>
+      </c>
+      <c r="N66" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B66, $C$2:$C$681, C66, $D$2:$D$681, D66, $E$2:$E$681, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O66" s="19"/>
-    </row>
-    <row r="67" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="6" t="s">
-        <v>61</v>
+    </row>
+    <row r="67" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="4">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="E67" s="4">
-        <v>3888</v>
+        <v>136.15</v>
       </c>
       <c r="F67" s="4">
-        <v>5.1948051949999998</v>
+        <v>-14.895611949999999</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="H67" s="5">
-        <v>3696</v>
+        <v>159.97999999999999</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="61"/>
+      <c r="J67" s="62" t="s">
+        <v>54</v>
+      </c>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
@@ -4560,39 +4557,38 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B67, $C$2:$C$681, C67, $D$2:$D$681, D67, $E$2:$E$681, E67) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O67" s="25"/>
-    </row>
-    <row r="68" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O67"/>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D68" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E68" s="4">
-        <v>1614</v>
+        <v>4014</v>
       </c>
       <c r="F68" s="4">
-        <v>5.4901960780000003</v>
+        <v>-15.01344456</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H68" s="5">
-        <v>1530</v>
+        <v>4723.1000000000004</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="63" t="s">
-        <v>40</v>
-      </c>
+      <c r="J68" s="62"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
@@ -4603,7 +4599,7 @@
       <c r="O68"/>
       <c r="P68"/>
     </row>
-    <row r="69" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="3">
         <v>46288.429861111108</v>
       </c>
@@ -4651,7 +4647,7 @@
       <c r="O69" s="10"/>
       <c r="P69" s="10"/>
     </row>
-    <row r="70" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="48">
         <v>46303.375</v>
       </c>
@@ -4699,7 +4695,7 @@
       <c r="O70" s="10"/>
       <c r="P70" s="10"/>
     </row>
-    <row r="71" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="48">
         <v>46296.40902777778</v>
       </c>
@@ -4713,7 +4709,7 @@
         <v>2</v>
       </c>
       <c r="E71" s="5">
-        <v>1584.1</v>
+        <v>1573</v>
       </c>
       <c r="F71" s="4">
         <v>5.7335469229999996</v>
@@ -4738,7 +4734,7 @@
       </c>
       <c r="M71" s="18">
         <f>ABS((D71*E71)-L71)</f>
-        <v>300</v>
+        <v>277.80000000000018</v>
       </c>
       <c r="N71" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B71, $C$2:$C$681, C71, $D$2:$D$681, D71, $E$2:$E$681, E71) &gt; 1, "Duplicate", "Unique")</f>
@@ -4747,30 +4743,30 @@
       <c r="O71" s="10"/>
       <c r="P71" s="10"/>
     </row>
-    <row r="72" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="3">
-        <v>46275.457638888889</v>
+    <row r="72" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E72" s="4">
-        <v>222</v>
+        <v>2752</v>
       </c>
       <c r="F72" s="4">
-        <v>5.8150619639999999</v>
+        <v>-17.133393559999998</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H72" s="5">
-        <v>209.8</v>
+        <v>3321</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>8</v>
@@ -4778,52 +4774,45 @@
       <c r="J72" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="K72" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="L72" s="18">
-        <v>56375</v>
-      </c>
-      <c r="M72" s="18">
-        <f>ABS((D72*E72)-L72)</f>
-        <v>34175</v>
-      </c>
-      <c r="N72" s="10" t="str">
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B72, $C$2:$C$681, C72, $D$2:$D$681, D72, $E$2:$E$681, E72) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O72"/>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D73" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E73" s="4">
-        <v>201</v>
+        <v>2660</v>
       </c>
       <c r="F73" s="4">
-        <v>5.8451816750000001</v>
+        <v>-19.903643479999999</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H73" s="5">
-        <v>189.9</v>
+        <v>3321</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="64" t="s">
-        <v>40</v>
-      </c>
+      <c r="J73" s="62"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
@@ -4834,7 +4823,7 @@
       <c r="O73"/>
       <c r="P73"/>
     </row>
-    <row r="74" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="48">
         <v>46304.375462962962</v>
       </c>
@@ -4929,7 +4918,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -4966,7 +4955,7 @@
       </c>
       <c r="P76"/>
     </row>
-    <row r="77" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="11">
         <v>46243.375</v>
       </c>
@@ -5013,7 +5002,7 @@
       </c>
       <c r="P77"/>
     </row>
-    <row r="78" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="48">
         <v>46293.375694444447</v>
       </c>
@@ -5108,7 +5097,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="48">
         <v>46293.401388888888</v>
       </c>
@@ -5154,7 +5143,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="48">
         <v>46293.375694444447</v>
       </c>
@@ -5200,7 +5189,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="58">
         <v>46302</v>
       </c>
@@ -5240,7 +5229,7 @@
       </c>
       <c r="O82"/>
     </row>
-    <row r="83" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>46301.375</v>
       </c>
@@ -5287,7 +5276,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="8" t="s">
         <v>61</v>
       </c>
@@ -5323,7 +5312,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="85" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46281.37777777778</v>
       </c>
@@ -5334,7 +5323,7 @@
         <v>7</v>
       </c>
       <c r="D85" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E85" s="4">
         <v>2320</v>
@@ -5362,7 +5351,7 @@
       </c>
       <c r="M85" s="18">
         <f>ABS((D85*E85)-L85)</f>
-        <v>810</v>
+        <v>1510</v>
       </c>
       <c r="N85" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B85, $C$2:$C$681, C85, $D$2:$D$681, D85, $E$2:$E$681, E85) &gt; 1, "Duplicate", "Unique")</f>
@@ -5371,7 +5360,7 @@
       <c r="O85" s="10"/>
       <c r="P85" s="10"/>
     </row>
-    <row r="86" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
         <v>46276.375</v>
       </c>
@@ -5417,7 +5406,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="48">
         <v>46303.375</v>
       </c>
@@ -5463,7 +5452,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="52">
         <v>46296.586111111108</v>
       </c>
@@ -5511,7 +5500,7 @@
       <c r="O88" s="29"/>
       <c r="P88" s="29"/>
     </row>
-    <row r="89" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="52">
         <v>46296.420138888891</v>
       </c>
@@ -5559,7 +5548,7 @@
       <c r="O89" s="29"/>
       <c r="P89" s="29"/>
     </row>
-    <row r="90" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="48">
         <v>46293.375694444447</v>
       </c>
@@ -5606,30 +5595,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="3">
-        <v>46261.375</v>
+    <row r="91" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D91" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4">
-        <v>204</v>
+        <v>2560</v>
       </c>
       <c r="F91" s="4">
-        <v>7.4249605059999997</v>
+        <v>-22.914784699999998</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H91" s="5">
-        <v>189.9</v>
+        <v>3321</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>8</v>
@@ -5637,22 +5626,17 @@
       <c r="J91" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="K91" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="L91" s="18">
-        <v>10550</v>
-      </c>
-      <c r="M91" s="18">
-        <f>ABS((D91*E91)-L91)</f>
-        <v>350</v>
-      </c>
-      <c r="N91" s="10" t="str">
+      <c r="K91" s="17"/>
+      <c r="L91" s="17"/>
+      <c r="M91" s="17"/>
+      <c r="N91" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B91, $C$2:$C$681, C91, $D$2:$D$681, D91, $E$2:$E$681, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O91"/>
+      <c r="P91"/>
+    </row>
+    <row r="92" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="11">
         <v>46243.375</v>
       </c>
@@ -5748,7 +5732,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="8" t="s">
         <v>61</v>
       </c>
@@ -5784,7 +5768,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -5830,7 +5814,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="48">
         <v>46293.375694444447</v>
       </c>
@@ -5877,35 +5861,35 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="3">
-        <v>46252.645138888889</v>
+    <row r="97" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D97" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E97" s="4">
-        <v>401</v>
+        <v>660</v>
       </c>
       <c r="F97" s="4">
-        <v>8.3930260850000007</v>
+        <v>-23.166472639999999</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="H97" s="5">
-        <v>369.95</v>
+        <v>859</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J97" s="65" t="s">
+      <c r="J97" s="62" t="s">
         <v>40</v>
       </c>
       <c r="K97" s="17"/>
@@ -5915,8 +5899,10 @@
         <f>IF(COUNTIFS( $B$2:$B$681, B97, $C$2:$C$681, C97, $D$2:$D$681, D97, $E$2:$E$681, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O97"/>
+      <c r="P97"/>
+    </row>
+    <row r="98" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30">
         <v>46272.451388888891</v>
       </c>
@@ -5962,7 +5948,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="99" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30">
         <v>46272.390972222223</v>
       </c>
@@ -6157,7 +6143,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>46286.375694444447</v>
       </c>
@@ -6204,7 +6190,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
         <v>46294.375</v>
       </c>
@@ -6250,7 +6236,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46267.461111111108</v>
       </c>
@@ -6296,7 +6282,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="48">
         <v>46289.390277777777</v>
       </c>
@@ -6342,7 +6328,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="48">
         <v>46293.375</v>
       </c>
@@ -6388,7 +6374,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="11">
         <v>46252.6875</v>
       </c>
@@ -6424,7 +6410,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3">
         <v>46275.375</v>
       </c>
@@ -6470,7 +6456,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="110" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3">
         <v>46267.375</v>
       </c>
@@ -6518,7 +6504,7 @@
       <c r="O110" s="10"/>
       <c r="P110" s="10"/>
     </row>
-    <row r="111" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="8" t="s">
         <v>61</v>
       </c>
@@ -6554,7 +6540,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -6600,7 +6586,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="8" t="s">
         <v>61</v>
       </c>
@@ -6634,7 +6620,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6731,7 +6717,7 @@
       </c>
       <c r="P115" s="10"/>
     </row>
-    <row r="116" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46266.375</v>
       </c>
@@ -6778,7 +6764,7 @@
       </c>
       <c r="P116" s="29"/>
     </row>
-    <row r="117" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -6874,7 +6860,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="48">
         <v>46289.375694444447</v>
       </c>
@@ -6920,7 +6906,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="120" spans="1:16" s="25" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:16" s="25" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="48">
         <v>46296.443055555559</v>
       </c>
@@ -6968,7 +6954,7 @@
       <c r="O120" s="10"/>
       <c r="P120" s="10"/>
     </row>
-    <row r="121" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -7016,7 +7002,7 @@
       <c r="O121"/>
       <c r="P121" s="29"/>
     </row>
-    <row r="122" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46267.38958333333</v>
       </c>
@@ -7062,7 +7048,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="123" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -7159,7 +7145,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7242,7 +7228,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="11">
         <v>46273.375</v>
       </c>
@@ -7288,7 +7274,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="128" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3">
         <v>46262.375</v>
       </c>
@@ -7335,7 +7321,7 @@
       </c>
       <c r="P128" s="10"/>
     </row>
-    <row r="129" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="8" t="s">
         <v>61</v>
       </c>
@@ -7374,7 +7360,7 @@
       <c r="O129" s="10"/>
       <c r="P129" s="10"/>
     </row>
-    <row r="130" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -7420,7 +7406,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -7466,7 +7452,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3">
         <v>46275.375</v>
       </c>
@@ -7540,7 +7526,7 @@
       <c r="I133" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J133" s="62" t="s">
+      <c r="J133" s="18" t="s">
         <v>116</v>
       </c>
       <c r="K133" s="18" t="s">
@@ -7561,7 +7547,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -7597,7 +7583,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46262.375</v>
       </c>
@@ -7643,7 +7629,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="136" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="8" t="s">
         <v>61</v>
       </c>
@@ -7679,7 +7665,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46261.375</v>
       </c>
@@ -7725,7 +7711,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
         <v>46261.375</v>
       </c>
@@ -7771,7 +7757,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="139" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7810,7 +7796,7 @@
       <c r="O139" s="24"/>
       <c r="P139" s="10"/>
     </row>
-    <row r="140" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46267.375</v>
       </c>
@@ -7858,7 +7844,7 @@
       <c r="O140" s="10"/>
       <c r="P140" s="19"/>
     </row>
-    <row r="141" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46274.375</v>
       </c>
@@ -7904,7 +7890,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -7950,7 +7936,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3">
         <v>46290.385416666664</v>
       </c>
@@ -7996,7 +7982,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46274.375</v>
       </c>
@@ -8042,7 +8028,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="11">
         <v>46253.375</v>
       </c>
@@ -8081,7 +8067,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="8" t="s">
         <v>61</v>
       </c>
@@ -8115,7 +8101,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="8" t="s">
         <v>61</v>
       </c>
@@ -8150,7 +8136,7 @@
       </c>
       <c r="P147" s="29"/>
     </row>
-    <row r="148" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>46252.6875</v>
       </c>
@@ -8186,7 +8172,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="30">
         <v>46335.62777777778</v>
       </c>
@@ -8234,7 +8220,7 @@
       <c r="O149" s="29"/>
       <c r="P149" s="29"/>
     </row>
-    <row r="150" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="30">
         <v>46280.375694444447</v>
       </c>
@@ -8472,7 +8458,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="155" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="33">
         <v>46255</v>
       </c>
@@ -8519,7 +8505,7 @@
       </c>
       <c r="P155" s="29"/>
     </row>
-    <row r="156" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="30">
         <v>46261.385416666664</v>
       </c>
@@ -8567,7 +8553,7 @@
       <c r="O156" s="10"/>
       <c r="P156" s="10"/>
     </row>
-    <row r="157" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3">
         <v>46260.375</v>
       </c>
@@ -8763,7 +8749,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -8809,7 +8795,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -8855,7 +8841,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="163" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8890,7 +8876,7 @@
       </c>
       <c r="O163" s="29"/>
     </row>
-    <row r="164" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="8" t="s">
         <v>61</v>
       </c>
@@ -8924,7 +8910,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="30">
         <v>46267.375</v>
       </c>
@@ -8970,7 +8956,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="166" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="30">
         <v>46267.375</v>
       </c>
@@ -9016,7 +9002,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9051,7 +9037,7 @@
       </c>
       <c r="P167" s="29"/>
     </row>
-    <row r="168" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="3">
         <v>46261.375</v>
       </c>
@@ -9098,7 +9084,7 @@
       </c>
       <c r="O168" s="29"/>
     </row>
-    <row r="169" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="8" t="s">
         <v>61</v>
       </c>
@@ -9134,7 +9120,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="30">
         <v>46265.375694444447</v>
       </c>
@@ -9180,7 +9166,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="30">
         <v>46266.375694444447</v>
       </c>
@@ -9226,7 +9212,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="172" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="30">
         <v>46267.424305555556</v>
       </c>
@@ -9274,7 +9260,7 @@
       <c r="O172" s="29"/>
       <c r="P172" s="29"/>
     </row>
-    <row r="173" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3">
         <v>46267.375</v>
       </c>
@@ -9320,7 +9306,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="174" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="11">
         <v>46252.6875</v>
       </c>
@@ -9357,7 +9343,7 @@
       </c>
       <c r="O174" s="29"/>
     </row>
-    <row r="175" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="8" t="s">
         <v>61</v>
       </c>
@@ -9398,7 +9384,7 @@
       <c r="O175" s="10"/>
       <c r="P175" s="10"/>
     </row>
-    <row r="176" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46294.375</v>
       </c>
@@ -9444,7 +9430,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="58">
         <v>46302</v>
       </c>
@@ -9534,7 +9520,7 @@
       </c>
       <c r="P178" s="29"/>
     </row>
-    <row r="179" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9716,7 +9702,7 @@
       </c>
       <c r="P182" s="29"/>
     </row>
-    <row r="183" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="8" t="s">
         <v>61</v>
       </c>
@@ -9752,7 +9738,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="184" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3">
         <v>46260.375</v>
       </c>
@@ -9898,7 +9884,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -9944,7 +9930,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="188" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="8" t="s">
         <v>61</v>
       </c>
@@ -9978,7 +9964,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -10024,7 +10010,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="190" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3">
         <v>46294.475694444445</v>
       </c>
@@ -10070,7 +10056,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10104,7 +10090,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="192" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10140,7 +10126,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="8" t="s">
         <v>61</v>
       </c>
@@ -10177,7 +10163,7 @@
       </c>
       <c r="O193" s="29"/>
     </row>
-    <row r="194" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3">
         <v>46259.375</v>
       </c>
@@ -10224,7 +10210,7 @@
       </c>
       <c r="O194" s="29"/>
     </row>
-    <row r="195" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="30">
         <v>46258.443749999999</v>
       </c>
@@ -10272,7 +10258,7 @@
       <c r="O195" s="29"/>
       <c r="P195" s="29"/>
     </row>
-    <row r="196" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="40">
         <v>46253.4</v>
       </c>
@@ -10315,7 +10301,7 @@
       <c r="O196" s="29"/>
       <c r="P196" s="29"/>
     </row>
-    <row r="197" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10351,7 +10337,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="198" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3">
         <v>46290.385416666664</v>
       </c>
@@ -10397,7 +10383,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="8" t="s">
         <v>61</v>
       </c>
@@ -10433,7 +10419,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="200" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10479,7 +10465,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10525,7 +10511,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="8" t="s">
         <v>61</v>
       </c>
@@ -10561,7 +10547,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10656,46 +10642,53 @@
         <v>239</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="6" t="s">
-        <v>61</v>
+    <row r="205" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A205" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D205" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E205" s="4">
-        <v>2435</v>
+        <v>726</v>
       </c>
       <c r="F205" s="4">
-        <v>18.873266940000001</v>
+        <v>-35.978835979999999</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>71</v>
+        <v>282</v>
       </c>
       <c r="H205" s="5">
-        <v>2048.4</v>
+        <v>1134</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J205" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="K205" s="17"/>
-      <c r="L205" s="17"/>
-      <c r="M205" s="17"/>
-      <c r="N205" t="str">
+        <v>40</v>
+      </c>
+      <c r="K205" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="L205" s="18">
+        <v>17940</v>
+      </c>
+      <c r="M205" s="18">
+        <f>ABS((D205*E205)-L205)</f>
+        <v>10680</v>
+      </c>
+      <c r="N205" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B205, $C$2:$C$681, C205, $D$2:$D$681, D205, $E$2:$E$681, E205) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="206" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10741,7 +10734,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -10787,7 +10780,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -10833,7 +10826,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="209" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="11">
         <v>46243.375</v>
       </c>
@@ -10919,7 +10912,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3">
         <v>46269.375</v>
       </c>
@@ -10965,7 +10958,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>46252.6875</v>
       </c>
@@ -11001,7 +10994,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3">
         <v>46262.375</v>
       </c>
@@ -11047,7 +11040,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="214" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -11093,7 +11086,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="20">
         <v>46255</v>
       </c>
@@ -11139,7 +11132,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3">
         <v>46276.4</v>
       </c>
@@ -11185,7 +11178,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="217" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>61</v>
       </c>
@@ -11221,7 +11214,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="218" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="30">
         <v>46260.556944444441</v>
       </c>
@@ -11267,7 +11260,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="219" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="30">
         <v>46261.375</v>
       </c>
@@ -11313,7 +11306,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="220" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46266.375</v>
       </c>
@@ -11359,7 +11352,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="221" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="30">
         <v>46258.443055555559</v>
       </c>
@@ -11407,7 +11400,7 @@
       <c r="O221" s="29"/>
       <c r="P221" s="29"/>
     </row>
-    <row r="222" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="30">
         <v>46259.375</v>
       </c>
@@ -11453,30 +11446,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="223" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="6" t="s">
-        <v>61</v>
+    <row r="223" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D223" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E223" s="4">
-        <v>2470</v>
+        <v>706</v>
       </c>
       <c r="F223" s="4">
-        <v>20.58191759</v>
+        <v>-37.742504410000002</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>71</v>
+        <v>282</v>
       </c>
       <c r="H223" s="5">
-        <v>2048.4</v>
+        <v>1134</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>8</v>
@@ -11484,17 +11477,24 @@
       <c r="J223" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="K223" s="17"/>
-      <c r="L223" s="17"/>
-      <c r="M223" s="17"/>
-      <c r="N223" t="str">
+      <c r="K223" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="L223" s="18">
+        <v>17940</v>
+      </c>
+      <c r="M223" s="18">
+        <f>ABS((D223*E223)-L223)</f>
+        <v>10880</v>
+      </c>
+      <c r="N223" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$681, B223, $C$2:$C$681, C223, $D$2:$D$681, D223, $E$2:$E$681, E223) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O223" s="10"/>
-      <c r="P223" s="24"/>
-    </row>
-    <row r="224" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P223" s="10"/>
+    </row>
+    <row r="224" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="42" t="s">
         <v>61</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="L224" s="43"/>
       <c r="M224" s="43"/>
       <c r="N224" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B224, $C$2:$C$681, C224, $D$2:$D$681, D224, $E$2:$E$681, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="0">IF(COUNTIFS( $B$2:$B$681, B224, $C$2:$C$681, C224, $D$2:$D$681, D224, $E$2:$E$681, E224) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O224" s="24"/>
@@ -11537,7 +11537,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>46252.6875</v>
       </c>
@@ -11569,11 +11569,11 @@
         <v>117</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B225, $C$2:$C$681, C225, $D$2:$D$681, D225, $E$2:$E$681, E225) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>61</v>
       </c>
@@ -11605,11 +11605,11 @@
         <v>117</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B226, $C$2:$C$681, C226, $D$2:$D$681, D226, $E$2:$E$681, E226) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="8" t="s">
         <v>61</v>
       </c>
@@ -11639,11 +11639,11 @@
       </c>
       <c r="J227" s="34"/>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B227, $C$2:$C$681, C227, $D$2:$D$681, D227, $E$2:$E$681, E227) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="8" t="s">
         <v>61</v>
       </c>
@@ -11675,12 +11675,12 @@
         <v>117</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B228, $C$2:$C$681, C228, $D$2:$D$681, D228, $E$2:$E$681, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="29"/>
     </row>
-    <row r="229" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="8" t="s">
         <v>61</v>
       </c>
@@ -11712,11 +11712,11 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B229, $C$2:$C$681, C229, $D$2:$D$681, D229, $E$2:$E$681, E229) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="8" t="s">
         <v>61</v>
       </c>
@@ -11748,11 +11748,11 @@
         <v>54</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B230, $C$2:$C$681, C230, $D$2:$D$681, D230, $E$2:$E$681, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="8" t="s">
         <v>61</v>
       </c>
@@ -11782,11 +11782,11 @@
       </c>
       <c r="J231" s="34"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B231, $C$2:$C$681, C231, $D$2:$D$681, D231, $E$2:$E$681, E231) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="8" t="s">
         <v>61</v>
       </c>
@@ -11818,12 +11818,12 @@
         <v>116</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B232, $C$2:$C$681, C232, $D$2:$D$681, D232, $E$2:$E$681, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P232" s="29"/>
     </row>
-    <row r="233" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3">
         <v>46276.390277777777</v>
       </c>
@@ -11865,11 +11865,11 @@
         <v>500</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B233, $C$2:$C$681, C233, $D$2:$D$681, D233, $E$2:$E$681, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -11901,11 +11901,11 @@
         <v>116</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B234, $C$2:$C$681, C234, $D$2:$D$681, D234, $E$2:$E$681, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="8" t="s">
         <v>61</v>
       </c>
@@ -11938,12 +11938,12 @@
       <c r="L235" s="18"/>
       <c r="M235" s="18"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B235, $C$2:$C$681, C235, $D$2:$D$681, D235, $E$2:$E$681, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="10"/>
     </row>
-    <row r="236" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="8" t="s">
         <v>61</v>
       </c>
@@ -11973,11 +11973,11 @@
       </c>
       <c r="J236" s="34"/>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B236, $C$2:$C$681, C236, $D$2:$D$681, D236, $E$2:$E$681, E236) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="8" t="s">
         <v>61</v>
       </c>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="J237" s="34"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B237, $C$2:$C$681, C237, $D$2:$D$681, D237, $E$2:$E$681, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12053,14 +12053,14 @@
         <v>800</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B238, $C$2:$C$681, C238, $D$2:$D$681, D238, $E$2:$E$681, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O238" s="38" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="239" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="8" t="s">
         <v>61</v>
       </c>
@@ -12093,13 +12093,13 @@
       <c r="L239" s="18"/>
       <c r="M239" s="18"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B239, $C$2:$C$681, C239, $D$2:$D$681, D239, $E$2:$E$681, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="10"/>
       <c r="P239" s="10"/>
     </row>
-    <row r="240" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -12141,11 +12141,11 @@
         <v>400</v>
       </c>
       <c r="N240" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B240, $C$2:$C$681, C240, $D$2:$D$681, D240, $E$2:$E$681, E240) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="8" t="s">
         <v>61</v>
       </c>
@@ -12175,11 +12175,11 @@
       </c>
       <c r="J241" s="34"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B241, $C$2:$C$681, C241, $D$2:$D$681, D241, $E$2:$E$681, E241) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3">
         <v>46276.388194444444</v>
       </c>
@@ -12221,11 +12221,11 @@
         <v>450</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B242, $C$2:$C$681, C242, $D$2:$D$681, D242, $E$2:$E$681, E242) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -12267,11 +12267,11 @@
         <v>300</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B243, $C$2:$C$681, C243, $D$2:$D$681, D243, $E$2:$E$681, E243) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="8" t="s">
         <v>61</v>
       </c>
@@ -12304,13 +12304,13 @@
       <c r="L244" s="18"/>
       <c r="M244" s="18"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B244, $C$2:$C$681, C244, $D$2:$D$681, D244, $E$2:$E$681, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="10"/>
       <c r="P244" s="10"/>
     </row>
-    <row r="245" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12345,13 +12345,13 @@
       <c r="L245" s="18"/>
       <c r="M245" s="18"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B245, $C$2:$C$681, C245, $D$2:$D$681, D245, $E$2:$E$681, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
       <c r="P245" s="10"/>
     </row>
-    <row r="246" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="3">
         <v>46276.375</v>
       </c>
@@ -12393,11 +12393,11 @@
         <v>816</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B246, $C$2:$C$681, C246, $D$2:$D$681, D246, $E$2:$E$681, E246) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -12439,12 +12439,12 @@
         <v>650</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B247, $C$2:$C$681, C247, $D$2:$D$681, D247, $E$2:$E$681, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P247" s="29"/>
     </row>
-    <row r="248" spans="1:16" s="29" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:16" s="29" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="8" t="s">
         <v>61</v>
       </c>
@@ -12479,13 +12479,13 @@
       <c r="L248" s="18"/>
       <c r="M248" s="18"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B248, $C$2:$C$681, C248, $D$2:$D$681, D248, $E$2:$E$681, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O248" s="10"/>
       <c r="P248" s="10"/>
     </row>
-    <row r="249" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="8" t="s">
         <v>61</v>
       </c>
@@ -12515,11 +12515,11 @@
       </c>
       <c r="J249" s="34"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B249, $C$2:$C$681, C249, $D$2:$D$681, D249, $E$2:$E$681, E249) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="J250" s="34"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B250, $C$2:$C$681, C250, $D$2:$D$681, D250, $E$2:$E$681, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="29"/>
     </row>
-    <row r="251" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="8" t="s">
         <v>61</v>
       </c>
@@ -12587,7 +12587,7 @@
       <c r="L251" s="18"/>
       <c r="M251" s="18"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B251, $C$2:$C$681, C251, $D$2:$D$681, D251, $E$2:$E$681, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="10"/>
@@ -12635,7 +12635,7 @@
         <v>48320</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B252, $C$2:$C$681, C252, $D$2:$D$681, D252, $E$2:$E$681, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="38" t="s">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="P252" s="10"/>
     </row>
-    <row r="253" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="3">
         <v>46274.375</v>
       </c>
@@ -12685,11 +12685,11 @@
         <v>651</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B253, $C$2:$C$681, C253, $D$2:$D$681, D253, $E$2:$E$681, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="3">
         <v>46262.375</v>
       </c>
@@ -12731,12 +12731,12 @@
         <v>370</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B254, $C$2:$C$681, C254, $D$2:$D$681, D254, $E$2:$E$681, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P254" s="29"/>
     </row>
-    <row r="255" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="48">
         <v>46304.375451388885</v>
       </c>
@@ -12778,11 +12778,11 @@
         <v>1000</v>
       </c>
       <c r="N255" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B255, $C$2:$C$681, C255, $D$2:$D$681, D255, $E$2:$E$681, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="8" t="s">
         <v>61</v>
       </c>
@@ -12812,12 +12812,12 @@
       </c>
       <c r="J256" s="34"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B256, $C$2:$C$681, C256, $D$2:$D$681, D256, $E$2:$E$681, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="29"/>
     </row>
-    <row r="257" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="8" t="s">
         <v>61</v>
       </c>
@@ -12849,11 +12849,11 @@
         <v>117</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B257, $C$2:$C$681, C257, $D$2:$D$681, D257, $E$2:$E$681, E257) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="8" t="s">
         <v>61</v>
       </c>
@@ -12883,11 +12883,11 @@
       </c>
       <c r="J258" s="34"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B258, $C$2:$C$681, C258, $D$2:$D$681, D258, $E$2:$E$681, E258) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N258:N307" si="1">IF(COUNTIFS( $B$2:$B$681, B258, $C$2:$C$681, C258, $D$2:$D$681, D258, $E$2:$E$681, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>61</v>
       </c>
@@ -12919,11 +12919,11 @@
         <v>116</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B259, $C$2:$C$681, C259, $D$2:$D$681, D259, $E$2:$E$681, E259) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -12965,12 +12965,12 @@
         <v>250</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B260, $C$2:$C$681, C260, $D$2:$D$681, D260, $E$2:$E$681, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P260" s="29"/>
     </row>
-    <row r="261" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -13005,11 +13005,11 @@
         <v>144</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B261, $C$2:$C$681, C261, $D$2:$D$681, D261, $E$2:$E$681, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="8" t="s">
         <v>61</v>
       </c>
@@ -13041,11 +13041,11 @@
         <v>116</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B262, $C$2:$C$681, C262, $D$2:$D$681, D262, $E$2:$E$681, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="3">
         <v>46290.385416666664</v>
       </c>
@@ -13087,11 +13087,11 @@
         <v>250</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B263, $C$2:$C$681, C263, $D$2:$D$681, D263, $E$2:$E$681, E263) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="8" t="s">
         <v>61</v>
       </c>
@@ -13123,11 +13123,11 @@
         <v>116</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B264, $C$2:$C$681, C264, $D$2:$D$681, D264, $E$2:$E$681, E264) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="3">
         <v>46276.375</v>
       </c>
@@ -13169,11 +13169,11 @@
         <v>450</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B265, $C$2:$C$681, C265, $D$2:$D$681, D265, $E$2:$E$681, E265) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="8" t="s">
         <v>61</v>
       </c>
@@ -13203,11 +13203,11 @@
       </c>
       <c r="J266" s="34"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B266, $C$2:$C$681, C266, $D$2:$D$681, D266, $E$2:$E$681, E266) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13245,15 +13245,15 @@
         <v>2260</v>
       </c>
       <c r="M267" s="18">
-        <f>ABS((D267*E267)-L267)</f>
+        <f t="shared" ref="M267:M274" si="2">ABS((D267*E267)-L267)</f>
         <v>235</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B267, $C$2:$C$681, C267, $D$2:$D$681, D267, $E$2:$E$681, E267) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="3">
         <v>46262.375</v>
       </c>
@@ -13291,11 +13291,11 @@
         <v>13300</v>
       </c>
       <c r="M268" s="18">
-        <f>ABS((D268*E268)-L268)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B268, $C$2:$C$681, C268, $D$2:$D$681, D268, $E$2:$E$681, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="10"/>
@@ -13339,11 +13339,11 @@
         <v>73800</v>
       </c>
       <c r="M269" s="18">
-        <f>ABS((D269*E269)-L269)</f>
+        <f t="shared" si="2"/>
         <v>47900</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B269, $C$2:$C$681, C269, $D$2:$D$681, D269, $E$2:$E$681, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="38" t="s">
@@ -13389,11 +13389,11 @@
         <v>25300</v>
       </c>
       <c r="M270" s="18">
-        <f>ABS((D270*E270)-L270)</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B270, $C$2:$C$681, C270, $D$2:$D$681, D270, $E$2:$E$681, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O270" s="38" t="s">
@@ -13438,18 +13438,18 @@
         <v>12480</v>
       </c>
       <c r="M271" s="18">
-        <f>ABS((D271*E271)-L271)</f>
+        <f t="shared" si="2"/>
         <v>495</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B271, $C$2:$C$681, C271, $D$2:$D$681, D271, $E$2:$E$681, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O271" s="38" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="272" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -13487,11 +13487,11 @@
         <v>20260</v>
       </c>
       <c r="M272" s="18">
-        <f>ABS((D272*E272)-L272)</f>
+        <f t="shared" si="2"/>
         <v>480</v>
       </c>
       <c r="N272" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B272, $C$2:$C$681, C272, $D$2:$D$681, D272, $E$2:$E$681, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13533,11 +13533,11 @@
         <v>25780</v>
       </c>
       <c r="M273" s="18">
-        <f>ABS((D273*E273)-L273)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B273, $C$2:$C$681, C273, $D$2:$D$681, D273, $E$2:$E$681, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="38" t="s">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="P273"/>
     </row>
-    <row r="274" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="3">
         <v>46268.375</v>
       </c>
@@ -13583,15 +13583,15 @@
         <v>25800</v>
       </c>
       <c r="M274" s="18">
-        <f>ABS((D274*E274)-L274)</f>
+        <f t="shared" si="2"/>
         <v>1800</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B274, $C$2:$C$681, C274, $D$2:$D$681, D274, $E$2:$E$681, E274) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="8" t="s">
         <v>61</v>
       </c>
@@ -13623,11 +13623,11 @@
         <v>116</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B275, $C$2:$C$681, C275, $D$2:$D$681, D275, $E$2:$E$681, E275) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -13669,13 +13669,13 @@
         <v>650</v>
       </c>
       <c r="N276" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B276, $C$2:$C$681, C276, $D$2:$D$681, D276, $E$2:$E$681, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O276"/>
       <c r="P276"/>
     </row>
-    <row r="277" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="8" t="s">
         <v>61</v>
       </c>
@@ -13707,11 +13707,11 @@
         <v>116</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B277, $C$2:$C$681, C277, $D$2:$D$681, D277, $E$2:$E$681, E277) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="8" t="s">
         <v>61</v>
       </c>
@@ -13743,11 +13743,11 @@
         <v>116</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B278, $C$2:$C$681, C278, $D$2:$D$681, D278, $E$2:$E$681, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -13789,11 +13789,11 @@
         <v>47480</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B279, $C$2:$C$681, C279, $D$2:$D$681, D279, $E$2:$E$681, E279) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -13835,11 +13835,11 @@
         <v>340</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B280, $C$2:$C$681, C280, $D$2:$D$681, D280, $E$2:$E$681, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="3">
         <v>46261.375</v>
       </c>
@@ -13881,11 +13881,11 @@
         <v>260</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B281, $C$2:$C$681, C281, $D$2:$D$681, D281, $E$2:$E$681, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="3">
         <v>46260.375</v>
       </c>
@@ -13927,11 +13927,11 @@
         <v>300</v>
       </c>
       <c r="N282" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B282, $C$2:$C$681, C282, $D$2:$D$681, D282, $E$2:$E$681, E282) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -13973,11 +13973,11 @@
         <v>300</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B283, $C$2:$C$681, C283, $D$2:$D$681, D283, $E$2:$E$681, E283) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="8" t="s">
         <v>61</v>
       </c>
@@ -14009,11 +14009,11 @@
         <v>117</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B284, $C$2:$C$681, C284, $D$2:$D$681, D284, $E$2:$E$681, E284) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="8" t="s">
         <v>61</v>
       </c>
@@ -14045,11 +14045,11 @@
         <v>117</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B285, $C$2:$C$681, C285, $D$2:$D$681, D285, $E$2:$E$681, E285) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="3">
         <v>46262.375</v>
       </c>
@@ -14091,11 +14091,11 @@
         <v>300</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B286, $C$2:$C$681, C286, $D$2:$D$681, D286, $E$2:$E$681, E286) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="8" t="s">
         <v>61</v>
       </c>
@@ -14125,11 +14125,11 @@
       </c>
       <c r="J287" s="34"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B287, $C$2:$C$681, C287, $D$2:$D$681, D287, $E$2:$E$681, E287) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -14166,11 +14166,11 @@
       <c r="L288" s="17"/>
       <c r="M288" s="17"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B288, $C$2:$C$681, C288, $D$2:$D$681, D288, $E$2:$E$681, E288) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="8" t="s">
         <v>61</v>
       </c>
@@ -14202,11 +14202,11 @@
         <v>116</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B289, $C$2:$C$681, C289, $D$2:$D$681, D289, $E$2:$E$681, E289) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="8" t="s">
         <v>61</v>
       </c>
@@ -14236,11 +14236,11 @@
       </c>
       <c r="J290" s="34"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B290, $C$2:$C$681, C290, $D$2:$D$681, D290, $E$2:$E$681, E290) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -14282,13 +14282,13 @@
         <v>285</v>
       </c>
       <c r="N291" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B291, $C$2:$C$681, C291, $D$2:$D$681, D291, $E$2:$E$681, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O291" s="10"/>
       <c r="P291" s="10"/>
     </row>
-    <row r="292" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="3">
         <v>46266.375</v>
       </c>
@@ -14330,11 +14330,11 @@
         <v>726</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B292, $C$2:$C$681, C292, $D$2:$D$681, D292, $E$2:$E$681, E292) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" s="29" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" s="29" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="11">
         <v>46252.6875</v>
       </c>
@@ -14369,13 +14369,13 @@
       <c r="L293" s="18"/>
       <c r="M293" s="18"/>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B293, $C$2:$C$681, C293, $D$2:$D$681, D293, $E$2:$E$681, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O293" s="10"/>
       <c r="P293" s="10"/>
     </row>
-    <row r="294" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="9" t="s">
         <v>61</v>
       </c>
@@ -14405,11 +14405,11 @@
       </c>
       <c r="J294" s="34"/>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B294, $C$2:$C$681, C294, $D$2:$D$681, D294, $E$2:$E$681, E294) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="11">
         <v>46252.6875</v>
       </c>
@@ -14441,11 +14441,11 @@
         <v>116</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B295, $C$2:$C$681, C295, $D$2:$D$681, D295, $E$2:$E$681, E295) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="8" t="s">
         <v>61</v>
       </c>
@@ -14475,11 +14475,11 @@
       </c>
       <c r="J296" s="34"/>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B296, $C$2:$C$681, C296, $D$2:$D$681, D296, $E$2:$E$681, E296) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="297" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -14521,11 +14521,11 @@
         <v>275</v>
       </c>
       <c r="N297" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B297, $C$2:$C$681, C297, $D$2:$D$681, D297, $E$2:$E$681, E297) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="298" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -14567,12 +14567,12 @@
         <v>250</v>
       </c>
       <c r="N298" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B298, $C$2:$C$681, C298, $D$2:$D$681, D298, $E$2:$E$681, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P298" s="29"/>
     </row>
-    <row r="299" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="8" t="s">
         <v>61</v>
       </c>
@@ -14602,11 +14602,11 @@
       </c>
       <c r="J299" s="34"/>
       <c r="N299" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B299, $C$2:$C$681, C299, $D$2:$D$681, D299, $E$2:$E$681, E299) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -14648,11 +14648,11 @@
         <v>250</v>
       </c>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B300, $C$2:$C$681, C300, $D$2:$D$681, D300, $E$2:$E$681, E300) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="301" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -14684,11 +14684,11 @@
         <v>54</v>
       </c>
       <c r="N301" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B301, $C$2:$C$681, C301, $D$2:$D$681, D301, $E$2:$E$681, E301) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="302" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -14730,11 +14730,11 @@
         <v>300</v>
       </c>
       <c r="N302" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B302, $C$2:$C$681, C302, $D$2:$D$681, D302, $E$2:$E$681, E302) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="303" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="11">
         <v>46252.6875</v>
       </c>
@@ -14766,11 +14766,11 @@
         <v>117</v>
       </c>
       <c r="N303" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B303, $C$2:$C$681, C303, $D$2:$D$681, D303, $E$2:$E$681, E303) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="304" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="11">
         <v>46252.6875</v>
       </c>
@@ -14802,11 +14802,11 @@
         <v>117</v>
       </c>
       <c r="N304" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B304, $C$2:$C$681, C304, $D$2:$D$681, D304, $E$2:$E$681, E304) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="305" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="41" t="s">
         <v>61</v>
       </c>
@@ -14841,13 +14841,13 @@
       <c r="L305" s="27"/>
       <c r="M305" s="27"/>
       <c r="N305" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B305, $C$2:$C$681, C305, $D$2:$D$681, D305, $E$2:$E$681, E305) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O305" s="29"/>
       <c r="P305" s="29"/>
     </row>
-    <row r="306" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="40">
         <v>46251.506249999999</v>
       </c>
@@ -14882,13 +14882,13 @@
       <c r="L306" s="27"/>
       <c r="M306" s="27"/>
       <c r="N306" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B306, $C$2:$C$681, C306, $D$2:$D$681, D306, $E$2:$E$681, E306) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O306" s="29"/>
       <c r="P306" s="29"/>
     </row>
-    <row r="307" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="8" t="s">
         <v>61</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>116</v>
       </c>
       <c r="N307" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B307, $C$2:$C$681, C307, $D$2:$D$681, D307, $E$2:$E$681, E307) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22353,14 +22353,14 @@
   <autoFilter ref="A1:P307" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="S"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
     <filterColumn colId="14">
       <filters blank="1"/>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P307">
-      <sortCondition ref="F1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P223">
+      <sortCondition descending="1" ref="F1:F307"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -22727,7 +22727,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B2, $C$2:$C$681, C2, $D$2:$D$681, D2, $E$2:$E$681, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$681, B2, $C$2:$C$681, C2, $D$2:$D$681, D2, $E$2:$E$681, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -22768,7 +22768,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B3, $C$2:$C$681, C3, $D$2:$D$681, D3, $E$2:$E$681, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22809,7 +22809,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B4, $C$2:$C$681, C4, $D$2:$D$681, D4, $E$2:$E$681, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -22857,7 +22857,7 @@
         <v>350</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B5, $C$2:$C$681, C5, $D$2:$D$681, D5, $E$2:$E$681, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22905,7 +22905,7 @@
         <v>34175</v>
       </c>
       <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B6, $C$2:$C$681, C6, $D$2:$D$681, D6, $E$2:$E$681, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -22946,7 +22946,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B7, $C$2:$C$681, C7, $D$2:$D$681, D7, $E$2:$E$681, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22983,7 +22983,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B8, $C$2:$C$681, C8, $D$2:$D$681, D8, $E$2:$E$681, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="25"/>
@@ -23024,7 +23024,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B9, $C$2:$C$681, C9, $D$2:$D$681, D9, $E$2:$E$681, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23061,7 +23061,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B10, $C$2:$C$681, C10, $D$2:$D$681, D10, $E$2:$E$681, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="19"/>
@@ -23100,7 +23100,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B11, $C$2:$C$681, C11, $D$2:$D$681, D11, $E$2:$E$681, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -23139,7 +23139,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B12, $C$2:$C$681, C12, $D$2:$D$681, D12, $E$2:$E$681, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -23180,7 +23180,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B13, $C$2:$C$681, C13, $D$2:$D$681, D13, $E$2:$E$681, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13"/>
@@ -23228,7 +23228,7 @@
         <v>500</v>
       </c>
       <c r="N14" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B14, $C$2:$C$681, C14, $D$2:$D$681, D14, $E$2:$E$681, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23265,7 +23265,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B15, $C$2:$C$681, C15, $D$2:$D$681, D15, $E$2:$E$681, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15"/>
@@ -23305,7 +23305,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B16, $C$2:$C$681, C16, $D$2:$D$681, D16, $E$2:$E$681, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23351,7 +23351,7 @@
         <v>300</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B17, $C$2:$C$681, C17, $D$2:$D$681, D17, $E$2:$E$681, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17"/>
@@ -23392,7 +23392,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B18, $C$2:$C$681, C18, $D$2:$D$681, D18, $E$2:$E$681, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -23433,7 +23433,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B19, $C$2:$C$681, C19, $D$2:$D$681, D19, $E$2:$E$681, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -23474,7 +23474,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B20, $C$2:$C$681, C20, $D$2:$D$681, D20, $E$2:$E$681, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -23513,7 +23513,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B21, $C$2:$C$681, C21, $D$2:$D$681, D21, $E$2:$E$681, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21"/>
@@ -23556,7 +23556,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B22, $C$2:$C$681, C22, $D$2:$D$681, D22, $E$2:$E$681, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -23604,7 +23604,7 @@
         <v>516</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B23, $C$2:$C$681, C23, $D$2:$D$681, D23, $E$2:$E$681, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
         <v>300</v>
       </c>
       <c r="N24" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B24, $C$2:$C$681, C24, $D$2:$D$681, D24, $E$2:$E$681, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P24" s="24"/>
@@ -23690,7 +23690,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B25, $C$2:$C$681, C25, $D$2:$D$681, D25, $E$2:$E$681, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B26, $C$2:$C$681, C26, $D$2:$D$681, D26, $E$2:$E$681, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -23777,7 +23777,7 @@
         <v>470</v>
       </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B27, $C$2:$C$681, C27, $D$2:$D$681, D27, $E$2:$E$681, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
         <v>225</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B28, $C$2:$C$681, C28, $D$2:$D$681, D28, $E$2:$E$681, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="10"/>
@@ -23865,7 +23865,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B29, $C$2:$C$681, C29, $D$2:$D$681, D29, $E$2:$E$681, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -23906,7 +23906,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B30, $C$2:$C$681, C30, $D$2:$D$681, D30, $E$2:$E$681, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P30"/>
@@ -23944,7 +23944,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B31, $C$2:$C$681, C31, $D$2:$D$681, D31, $E$2:$E$681, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -23992,7 +23992,7 @@
         <v>440</v>
       </c>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B32, $C$2:$C$681, C32, $D$2:$D$681, D32, $E$2:$E$681, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24029,7 +24029,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B33, $C$2:$C$681, C33, $D$2:$D$681, D33, $E$2:$E$681, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -24070,7 +24070,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B34, $C$2:$C$681, C34, $D$2:$D$681, D34, $E$2:$E$681, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -24112,7 +24112,7 @@
         <v>3156</v>
       </c>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B35, $C$2:$C$681, C35, $D$2:$D$681, D35, $E$2:$E$681, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P35" s="19"/>
@@ -24150,7 +24150,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B36, $C$2:$C$681, C36, $D$2:$D$681, D36, $E$2:$E$681, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -24189,7 +24189,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B37, $C$2:$C$681, C37, $D$2:$D$681, D37, $E$2:$E$681, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -24228,7 +24228,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B38, $C$2:$C$681, C38, $D$2:$D$681, D38, $E$2:$E$681, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -24276,7 +24276,7 @@
         <v>253</v>
       </c>
       <c r="N39" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B39, $C$2:$C$681, C39, $D$2:$D$681, D39, $E$2:$E$681, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24323,7 +24323,7 @@
         <v>540</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B40, $C$2:$C$681, C40, $D$2:$D$681, D40, $E$2:$E$681, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -24362,7 +24362,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B41, $C$2:$C$681, C41, $D$2:$D$681, D41, $E$2:$E$681, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B42, $C$2:$C$681, C42, $D$2:$D$681, D42, $E$2:$E$681, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24446,7 +24446,7 @@
         <v>448</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B43, $C$2:$C$681, C43, $D$2:$D$681, D43, $E$2:$E$681, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="10"/>
@@ -24485,7 +24485,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B44, $C$2:$C$681, C44, $D$2:$D$681, D44, $E$2:$E$681, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24524,7 +24524,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B45, $C$2:$C$681, C45, $D$2:$D$681, D45, $E$2:$E$681, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24570,7 +24570,7 @@
         <v>420</v>
       </c>
       <c r="N46" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B46, $C$2:$C$681, C46, $D$2:$D$681, D46, $E$2:$E$681, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P46" s="10"/>
@@ -24608,7 +24608,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B47, $C$2:$C$681, C47, $D$2:$D$681, D47, $E$2:$E$681, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -24647,7 +24647,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B48, $C$2:$C$681, C48, $D$2:$D$681, D48, $E$2:$E$681, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -24695,7 +24695,7 @@
         <v>264</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B49, $C$2:$C$681, C49, $D$2:$D$681, D49, $E$2:$E$681, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="10"/>
@@ -24734,7 +24734,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B50, $C$2:$C$681, C50, $D$2:$D$681, D50, $E$2:$E$681, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -24775,7 +24775,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B51, $C$2:$C$681, C51, $D$2:$D$681, D51, $E$2:$E$681, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -24813,7 +24813,7 @@
         <v>116</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B52, $C$2:$C$681, C52, $D$2:$D$681, D52, $E$2:$E$681, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24859,7 +24859,7 @@
         <v>550</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B53, $C$2:$C$681, C53, $D$2:$D$681, D53, $E$2:$E$681, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24905,7 +24905,7 @@
         <v>414</v>
       </c>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B54, $C$2:$C$681, C54, $D$2:$D$681, D54, $E$2:$E$681, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="10"/>
@@ -24953,7 +24953,7 @@
         <v>840</v>
       </c>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B55, $C$2:$C$681, C55, $D$2:$D$681, D55, $E$2:$E$681, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="10"/>
@@ -24994,7 +24994,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B56, $C$2:$C$681, C56, $D$2:$D$681, D56, $E$2:$E$681, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -25032,7 +25032,7 @@
         <v>117</v>
       </c>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B57, $C$2:$C$681, C57, $D$2:$D$681, D57, $E$2:$E$681, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P57"/>
@@ -25070,7 +25070,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B58, $C$2:$C$681, C58, $D$2:$D$681, D58, $E$2:$E$681, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -25114,11 +25114,11 @@
         <v>6202</v>
       </c>
       <c r="M59" s="43">
-        <f t="shared" ref="M59:M65" si="0">ABS((D59*E59)-L59)</f>
+        <f t="shared" ref="M59:M65" si="1">ABS((D59*E59)-L59)</f>
         <v>296</v>
       </c>
       <c r="N59" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B59, $C$2:$C$681, C59, $D$2:$D$681, D59, $E$2:$E$681, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P59" s="24" t="s">
@@ -25163,11 +25163,11 @@
         <v>8400</v>
       </c>
       <c r="M60" s="18">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="N60" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B60, $C$2:$C$681, C60, $D$2:$D$681, D60, $E$2:$E$681, E60) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25209,11 +25209,11 @@
         <v>3395</v>
       </c>
       <c r="M61" s="18">
+        <f t="shared" si="1"/>
+        <v>295</v>
+      </c>
+      <c r="N61" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>295</v>
-      </c>
-      <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B61, $C$2:$C$681, C61, $D$2:$D$681, D61, $E$2:$E$681, E61) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25255,11 +25255,11 @@
         <v>16832</v>
       </c>
       <c r="M62" s="18">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="N62" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>650</v>
-      </c>
-      <c r="N62" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B62, $C$2:$C$681, C62, $D$2:$D$681, D62, $E$2:$E$681, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25301,11 +25301,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M63" s="18">
+        <f t="shared" si="1"/>
+        <v>11409.000000000004</v>
+      </c>
+      <c r="N63" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>11409.000000000004</v>
-      </c>
-      <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B63, $C$2:$C$681, C63, $D$2:$D$681, D63, $E$2:$E$681, E63) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O63" s="10"/>
@@ -25349,11 +25349,11 @@
         <v>12800</v>
       </c>
       <c r="M64" s="18">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="N64" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>650</v>
-      </c>
-      <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B64, $C$2:$C$681, C64, $D$2:$D$681, D64, $E$2:$E$681, E64) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25395,11 +25395,11 @@
         <v>4640</v>
       </c>
       <c r="M65" s="18">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="N65" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B65, $C$2:$C$681, C65, $D$2:$D$681, D65, $E$2:$E$681, E65) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O65" s="38" t="s">
@@ -25439,7 +25439,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B66, $C$2:$C$681, C66, $D$2:$D$681, D66, $E$2:$E$681, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="2">IF(COUNTIFS( $B$2:$B$681, B66, $C$2:$C$681, C66, $D$2:$D$681, D66, $E$2:$E$681, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -25487,7 +25487,7 @@
         <v>720</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B67, $C$2:$C$681, C67, $D$2:$D$681, D67, $E$2:$E$681, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B68, $C$2:$C$681, C68, $D$2:$D$681, D68, $E$2:$E$681, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -25567,7 +25567,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B69, $C$2:$C$681, C69, $D$2:$D$681, D69, $E$2:$E$681, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -25615,7 +25615,7 @@
         <v>500</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B70, $C$2:$C$681, C70, $D$2:$D$681, D70, $E$2:$E$681, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="10"/>
@@ -25656,7 +25656,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B71, $C$2:$C$681, C71, $D$2:$D$681, D71, $E$2:$E$681, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
@@ -25700,11 +25700,11 @@
         <v>3560</v>
       </c>
       <c r="M72" s="18">
-        <f t="shared" ref="M72:M77" si="1">ABS((D72*E72)-L72)</f>
+        <f t="shared" ref="M72:M77" si="3">ABS((D72*E72)-L72)</f>
         <v>250</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B72, $C$2:$C$681, C72, $D$2:$D$681, D72, $E$2:$E$681, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25746,11 +25746,11 @@
         <v>3245</v>
       </c>
       <c r="M73" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>240</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B73, $C$2:$C$681, C73, $D$2:$D$681, D73, $E$2:$E$681, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25792,11 +25792,11 @@
         <v>6127.5</v>
       </c>
       <c r="M74" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>612.5</v>
       </c>
       <c r="N74" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B74, $C$2:$C$681, C74, $D$2:$D$681, D74, $E$2:$E$681, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O74" s="29"/>
@@ -25840,11 +25840,11 @@
         <v>6320</v>
       </c>
       <c r="M75" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="N75" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B75, $C$2:$C$681, C75, $D$2:$D$681, D75, $E$2:$E$681, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O75" s="29"/>
@@ -25889,11 +25889,11 @@
         <v>8870</v>
       </c>
       <c r="M76" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B76, $C$2:$C$681, C76, $D$2:$D$681, D76, $E$2:$E$681, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25935,11 +25935,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M77" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14149.000000000004</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B77, $C$2:$C$681, C77, $D$2:$D$681, D77, $E$2:$E$681, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P77"/>
@@ -25977,7 +25977,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B78, $C$2:$C$681, C78, $D$2:$D$681, D78, $E$2:$E$681, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -26026,7 +26026,7 @@
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B79, $C$2:$C$681, C79, $D$2:$D$681, D79, $E$2:$E$681, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26072,7 +26072,7 @@
         <v>1200</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B80, $C$2:$C$681, C80, $D$2:$D$681, D80, $E$2:$E$681, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="38" t="s">
@@ -26121,7 +26121,7 @@
         <v>650</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B81, $C$2:$C$681, C81, $D$2:$D$681, D81, $E$2:$E$681, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="38" t="s">
@@ -26160,7 +26160,7 @@
         <v>117</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B82, $C$2:$C$681, C82, $D$2:$D$681, D82, $E$2:$E$681, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26196,7 +26196,7 @@
         <v>116</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B83, $C$2:$C$681, C83, $D$2:$D$681, D83, $E$2:$E$681, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26235,7 +26235,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B84, $C$2:$C$681, C84, $D$2:$D$681, D84, $E$2:$E$681, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O84"/>
@@ -26283,7 +26283,7 @@
         <v>250</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B85, $C$2:$C$681, C85, $D$2:$D$681, D85, $E$2:$E$681, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="10"/>
@@ -26331,7 +26331,7 @@
         <v>250</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B86, $C$2:$C$681, C86, $D$2:$D$681, D86, $E$2:$E$681, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26370,7 +26370,7 @@
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B87, $C$2:$C$681, C87, $D$2:$D$681, D87, $E$2:$E$681, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O87"/>
@@ -26418,7 +26418,7 @@
         <v>300</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B88, $C$2:$C$681, C88, $D$2:$D$681, D88, $E$2:$E$681, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="J89" s="34"/>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B89, $C$2:$C$681, C89, $D$2:$D$681, D89, $E$2:$E$681, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26488,7 +26488,7 @@
         <v>117</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B90, $C$2:$C$681, C90, $D$2:$D$681, D90, $E$2:$E$681, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26531,11 +26531,11 @@
         <v>8970</v>
       </c>
       <c r="M91" s="18">
-        <f t="shared" ref="M91:M98" si="2">ABS((D91*E91)-L91)</f>
+        <f t="shared" ref="M91:M98" si="4">ABS((D91*E91)-L91)</f>
         <v>300</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B91, $C$2:$C$681, C91, $D$2:$D$681, D91, $E$2:$E$681, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26577,11 +26577,11 @@
         <v>9886</v>
       </c>
       <c r="M92" s="18">
+        <f t="shared" si="4"/>
+        <v>654</v>
+      </c>
+      <c r="N92" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>654</v>
-      </c>
-      <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B92, $C$2:$C$681, C92, $D$2:$D$681, D92, $E$2:$E$681, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26623,11 +26623,11 @@
         <v>32900</v>
       </c>
       <c r="M93" s="18">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="N93" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B93, $C$2:$C$681, C93, $D$2:$D$681, D93, $E$2:$E$681, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26669,11 +26669,11 @@
         <v>8220</v>
       </c>
       <c r="M94" s="18">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="N94" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>360</v>
-      </c>
-      <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B94, $C$2:$C$681, C94, $D$2:$D$681, D94, $E$2:$E$681, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O94" s="38" t="s">
@@ -26718,11 +26718,11 @@
         <v>18140</v>
       </c>
       <c r="M95" s="26">
+        <f t="shared" si="4"/>
+        <v>650</v>
+      </c>
+      <c r="N95" t="str">
         <f t="shared" si="2"/>
-        <v>650</v>
-      </c>
-      <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B95, $C$2:$C$681, C95, $D$2:$D$681, D95, $E$2:$E$681, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26764,11 +26764,11 @@
         <v>16755</v>
       </c>
       <c r="M96" s="18">
+        <f t="shared" si="4"/>
+        <v>295</v>
+      </c>
+      <c r="N96" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>295</v>
-      </c>
-      <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B96, $C$2:$C$681, C96, $D$2:$D$681, D96, $E$2:$E$681, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26810,11 +26810,11 @@
         <v>2868.2</v>
       </c>
       <c r="M97" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N97" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B97, $C$2:$C$681, C97, $D$2:$D$681, D97, $E$2:$E$681, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26856,11 +26856,11 @@
         <v>9170</v>
       </c>
       <c r="M98" s="27">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="N98" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>200</v>
-      </c>
-      <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B98, $C$2:$C$681, C98, $D$2:$D$681, D98, $E$2:$E$681, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O98" s="38" t="s">
@@ -26903,7 +26903,7 @@
       <c r="L99" s="18"/>
       <c r="M99" s="18"/>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B99, $C$2:$C$681, C99, $D$2:$D$681, D99, $E$2:$E$681, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="10"/>
@@ -26947,11 +26947,11 @@
         <v>5450</v>
       </c>
       <c r="M100" s="18">
-        <f t="shared" ref="M100:M110" si="3">ABS((D100*E100)-L100)</f>
+        <f t="shared" ref="M100:M110" si="5">ABS((D100*E100)-L100)</f>
         <v>265</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B100, $C$2:$C$681, C100, $D$2:$D$681, D100, $E$2:$E$681, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26994,11 +26994,11 @@
         <v>6900</v>
       </c>
       <c r="M101" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>444</v>
       </c>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B101, $C$2:$C$681, C101, $D$2:$D$681, D101, $E$2:$E$681, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27040,11 +27040,11 @@
         <v>9902</v>
       </c>
       <c r="M102" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>646</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B102, $C$2:$C$681, C102, $D$2:$D$681, D102, $E$2:$E$681, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="38" t="s">
@@ -27089,11 +27089,11 @@
         <v>39300</v>
       </c>
       <c r="M103" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18850</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B103, $C$2:$C$681, C103, $D$2:$D$681, D103, $E$2:$E$681, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>15075</v>
       </c>
       <c r="M104" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>645</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B104, $C$2:$C$681, C104, $D$2:$D$681, D104, $E$2:$E$681, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="38" t="s">
@@ -27184,11 +27184,11 @@
         <v>19730.5</v>
       </c>
       <c r="M105" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>504.5</v>
       </c>
       <c r="N105" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B105, $C$2:$C$681, C105, $D$2:$D$681, D105, $E$2:$E$681, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O105" s="38" t="s">
@@ -27234,11 +27234,11 @@
         <v>19690</v>
       </c>
       <c r="M106" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>545</v>
       </c>
       <c r="N106" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B106, $C$2:$C$681, C106, $D$2:$D$681, D106, $E$2:$E$681, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O106" s="38" t="s">
@@ -27284,11 +27284,11 @@
         <v>17040</v>
       </c>
       <c r="M107" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>880</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B107, $C$2:$C$681, C107, $D$2:$D$681, D107, $E$2:$E$681, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="38" t="s">
@@ -27333,11 +27333,11 @@
         <v>20070</v>
       </c>
       <c r="M108" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>810</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B108, $C$2:$C$681, C108, $D$2:$D$681, D108, $E$2:$E$681, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27379,11 +27379,11 @@
         <v>8820</v>
       </c>
       <c r="M109" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N109" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B109, $C$2:$C$681, C109, $D$2:$D$681, D109, $E$2:$E$681, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="29"/>
@@ -27427,11 +27427,11 @@
         <v>36946</v>
       </c>
       <c r="M110" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>934</v>
       </c>
       <c r="N110" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B110, $C$2:$C$681, C110, $D$2:$D$681, D110, $E$2:$E$681, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
         <v>117</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B111, $C$2:$C$681, C111, $D$2:$D$681, D111, $E$2:$E$681, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>33200</v>
       </c>
       <c r="M112" s="18">
-        <f t="shared" ref="M112:M127" si="4">ABS((D112*E112)-L112)</f>
+        <f t="shared" ref="M112:M127" si="6">ABS((D112*E112)-L112)</f>
         <v>1200</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B112, $C$2:$C$681, C112, $D$2:$D$681, D112, $E$2:$E$681, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27555,11 +27555,11 @@
         <v>11660</v>
       </c>
       <c r="M113" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B113, $C$2:$C$681, C113, $D$2:$D$681, D113, $E$2:$E$681, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="38" t="s">
@@ -27604,11 +27604,11 @@
         <v>9170</v>
       </c>
       <c r="M114" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B114, $C$2:$C$681, C114, $D$2:$D$681, D114, $E$2:$E$681, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27650,11 +27650,11 @@
         <v>3300</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B115, $C$2:$C$681, C115, $D$2:$D$681, D115, $E$2:$E$681, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="10"/>
@@ -27698,11 +27698,11 @@
         <v>8420</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B116, $C$2:$C$681, C116, $D$2:$D$681, D116, $E$2:$E$681, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27744,11 +27744,11 @@
         <v>10250</v>
       </c>
       <c r="M117" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B117, $C$2:$C$681, C117, $D$2:$D$681, D117, $E$2:$E$681, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27790,11 +27790,11 @@
         <v>10725.5</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>654.5</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B118, $C$2:$C$681, C118, $D$2:$D$681, D118, $E$2:$E$681, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27836,11 +27836,11 @@
         <v>20010</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>450</v>
       </c>
       <c r="N119" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B119, $C$2:$C$681, C119, $D$2:$D$681, D119, $E$2:$E$681, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P119"/>
@@ -27883,11 +27883,11 @@
         <v>10300</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B120, $C$2:$C$681, C120, $D$2:$D$681, D120, $E$2:$E$681, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="10"/>
@@ -27931,11 +27931,11 @@
         <v>3810</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B121, $C$2:$C$681, C121, $D$2:$D$681, D121, $E$2:$E$681, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27977,11 +27977,11 @@
         <v>33950</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>850</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B122, $C$2:$C$681, C122, $D$2:$D$681, D122, $E$2:$E$681, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28023,11 +28023,11 @@
         <v>20260</v>
       </c>
       <c r="M123" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N123" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B123, $C$2:$C$681, C123, $D$2:$D$681, D123, $E$2:$E$681, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O123"/>
@@ -28070,11 +28070,11 @@
         <v>9270</v>
       </c>
       <c r="M124" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B124, $C$2:$C$681, C124, $D$2:$D$681, D124, $E$2:$E$681, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P124" s="19"/>
@@ -28117,11 +28117,11 @@
         <v>37480</v>
       </c>
       <c r="M125" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="N125" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B125, $C$2:$C$681, C125, $D$2:$D$681, D125, $E$2:$E$681, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P125" s="29"/>
@@ -28164,11 +28164,11 @@
         <v>17150</v>
       </c>
       <c r="M126" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B126, $C$2:$C$681, C126, $D$2:$D$681, D126, $E$2:$E$681, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28210,11 +28210,11 @@
         <v>4200</v>
       </c>
       <c r="M127" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>290</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B127, $C$2:$C$681, C127, $D$2:$D$681, D127, $E$2:$E$681, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28251,7 +28251,7 @@
       <c r="L128" s="18"/>
       <c r="M128" s="18"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B128, $C$2:$C$681, C128, $D$2:$D$681, D128, $E$2:$E$681, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -28299,7 +28299,7 @@
         <v>320</v>
       </c>
       <c r="N129" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B129, $C$2:$C$681, C129, $D$2:$D$681, D129, $E$2:$E$681, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28345,7 +28345,7 @@
         <v>235</v>
       </c>
       <c r="N130" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B130, $C$2:$C$681, C130, $D$2:$D$681, D130, $E$2:$E$681, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="7">IF(COUNTIFS( $B$2:$B$681, B130, $C$2:$C$681, C130, $D$2:$D$681, D130, $E$2:$E$681, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="29"/>
@@ -28381,7 +28381,7 @@
       </c>
       <c r="J131" s="34"/>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B131, $C$2:$C$681, C131, $D$2:$D$681, D131, $E$2:$E$681, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
         <v>300</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B132, $C$2:$C$681, C132, $D$2:$D$681, D132, $E$2:$E$681, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="29"/>
@@ -28464,7 +28464,7 @@
         <v>116</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B133, $C$2:$C$681, C133, $D$2:$D$681, D133, $E$2:$E$681, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28510,7 +28510,7 @@
         <v>18350</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B134, $C$2:$C$681, C134, $D$2:$D$681, D134, $E$2:$E$681, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28556,7 +28556,7 @@
         <v>300</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B135, $C$2:$C$681, C135, $D$2:$D$681, D135, $E$2:$E$681, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28590,7 +28590,7 @@
       </c>
       <c r="J136" s="34"/>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B136, $C$2:$C$681, C136, $D$2:$D$681, D136, $E$2:$E$681, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28636,7 +28636,7 @@
         <v>300</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B137, $C$2:$C$681, C137, $D$2:$D$681, D137, $E$2:$E$681, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28672,7 +28672,7 @@
         <v>117</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B138, $C$2:$C$681, C138, $D$2:$D$681, D138, $E$2:$E$681, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28713,7 +28713,7 @@
       <c r="L139" s="18"/>
       <c r="M139" s="18"/>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B139, $C$2:$C$681, C139, $D$2:$D$681, D139, $E$2:$E$681, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="10"/>
@@ -28761,7 +28761,7 @@
         <v>940</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B140, $C$2:$C$681, C140, $D$2:$D$681, D140, $E$2:$E$681, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="10"/>
@@ -28809,7 +28809,7 @@
         <v>268</v>
       </c>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B141, $C$2:$C$681, C141, $D$2:$D$681, D141, $E$2:$E$681, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28855,7 +28855,7 @@
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B142, $C$2:$C$681, C142, $D$2:$D$681, D142, $E$2:$E$681, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="J143" s="34"/>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B143, $C$2:$C$681, C143, $D$2:$D$681, D143, $E$2:$E$681, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="24"/>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="J144" s="34"/>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B144, $C$2:$C$681, C144, $D$2:$D$681, D144, $E$2:$E$681, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28970,7 +28970,7 @@
         <v>250</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B145, $C$2:$C$681, C145, $D$2:$D$681, D145, $E$2:$E$681, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29004,7 +29004,7 @@
       </c>
       <c r="J146" s="34"/>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B146, $C$2:$C$681, C146, $D$2:$D$681, D146, $E$2:$E$681, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="38" t="s">
@@ -29054,7 +29054,7 @@
         <v>300</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B147, $C$2:$C$681, C147, $D$2:$D$681, D147, $E$2:$E$681, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="J148" s="34"/>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B148, $C$2:$C$681, C148, $D$2:$D$681, D148, $E$2:$E$681, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P148" s="29"/>
@@ -29135,7 +29135,7 @@
         <v>395</v>
       </c>
       <c r="N149" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B149, $C$2:$C$681, C149, $D$2:$D$681, D149, $E$2:$E$681, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="38" t="s">
@@ -29185,7 +29185,7 @@
         <v>250</v>
       </c>
       <c r="N150" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B150, $C$2:$C$681, C150, $D$2:$D$681, D150, $E$2:$E$681, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O150" s="38" t="s">
@@ -29226,7 +29226,7 @@
       <c r="L151" s="18"/>
       <c r="M151" s="18"/>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B151, $C$2:$C$681, C151, $D$2:$D$681, D151, $E$2:$E$681, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P151" s="10"/>
@@ -29266,7 +29266,7 @@
       <c r="L152" s="17"/>
       <c r="M152" s="17"/>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B152, $C$2:$C$681, C152, $D$2:$D$681, D152, $E$2:$E$681, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O152"/>
@@ -29313,7 +29313,7 @@
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B153, $C$2:$C$681, C153, $D$2:$D$681, D153, $E$2:$E$681, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29359,7 +29359,7 @@
         <v>1700</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B154, $C$2:$C$681, C154, $D$2:$D$681, D154, $E$2:$E$681, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="29"/>
@@ -29406,7 +29406,7 @@
         <v>500</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B155, $C$2:$C$681, C155, $D$2:$D$681, D155, $E$2:$E$681, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O155" s="39" t="s">
@@ -29446,7 +29446,7 @@
       <c r="L156" s="18"/>
       <c r="M156" s="18"/>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B156, $C$2:$C$681, C156, $D$2:$D$681, D156, $E$2:$E$681, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O156" s="10"/>
@@ -29483,7 +29483,7 @@
         <v>117</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B157, $C$2:$C$681, C157, $D$2:$D$681, D157, $E$2:$E$681, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29529,7 +29529,7 @@
         <v>800</v>
       </c>
       <c r="N158" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B158, $C$2:$C$681, C158, $D$2:$D$681, D158, $E$2:$E$681, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29565,7 +29565,7 @@
         <v>116</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B159, $C$2:$C$681, C159, $D$2:$D$681, D159, $E$2:$E$681, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29607,11 +29607,11 @@
         <v>5520</v>
       </c>
       <c r="M160" s="27">
-        <f t="shared" ref="M160:M175" si="5">ABS((D160*E160)-L160)</f>
+        <f t="shared" ref="M160:M175" si="8">ABS((D160*E160)-L160)</f>
         <v>300</v>
       </c>
       <c r="N160" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B160, $C$2:$C$681, C160, $D$2:$D$681, D160, $E$2:$E$681, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="38" t="s">
@@ -29656,11 +29656,11 @@
         <v>2657</v>
       </c>
       <c r="M161" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>253</v>
       </c>
       <c r="N161" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B161, $C$2:$C$681, C161, $D$2:$D$681, D161, $E$2:$E$681, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O161" s="38" t="s">
@@ -29705,11 +29705,11 @@
         <v>2554.5</v>
       </c>
       <c r="M162" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>355.5</v>
       </c>
       <c r="N162" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B162, $C$2:$C$681, C162, $D$2:$D$681, D162, $E$2:$E$681, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O162" s="38" t="s">
@@ -29755,11 +29755,11 @@
         <v>5755</v>
       </c>
       <c r="M163" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>275</v>
       </c>
       <c r="N163" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B163, $C$2:$C$681, C163, $D$2:$D$681, D163, $E$2:$E$681, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29801,11 +29801,11 @@
         <v>5805</v>
       </c>
       <c r="M164" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>225</v>
       </c>
       <c r="N164" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B164, $C$2:$C$681, C164, $D$2:$D$681, D164, $E$2:$E$681, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29847,11 +29847,11 @@
         <v>7578</v>
       </c>
       <c r="M165" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N165" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B165, $C$2:$C$681, C165, $D$2:$D$681, D165, $E$2:$E$681, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29893,11 +29893,11 @@
         <v>7578</v>
       </c>
       <c r="M166" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N166" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B166, $C$2:$C$681, C166, $D$2:$D$681, D166, $E$2:$E$681, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29939,11 +29939,11 @@
         <v>4968</v>
       </c>
       <c r="M167" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>280</v>
       </c>
       <c r="N167" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B167, $C$2:$C$681, C167, $D$2:$D$681, D167, $E$2:$E$681, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O167" s="29"/>
@@ -29987,11 +29987,11 @@
         <v>4680</v>
       </c>
       <c r="M168" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="N168" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B168, $C$2:$C$681, C168, $D$2:$D$681, D168, $E$2:$E$681, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="P168" s="29"/>
@@ -30034,11 +30034,11 @@
         <v>4520</v>
       </c>
       <c r="M169" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N169" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B169, $C$2:$C$681, C169, $D$2:$D$681, D169, $E$2:$E$681, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30080,11 +30080,11 @@
         <v>5940</v>
       </c>
       <c r="M170" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B170, $C$2:$C$681, C170, $D$2:$D$681, D170, $E$2:$E$681, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30126,11 +30126,11 @@
         <v>8480</v>
       </c>
       <c r="M171" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>280</v>
       </c>
       <c r="N171" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B171, $C$2:$C$681, C171, $D$2:$D$681, D171, $E$2:$E$681, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O171" s="38" t="s">
@@ -30175,11 +30175,11 @@
         <v>5290</v>
       </c>
       <c r="M172" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N172" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B172, $C$2:$C$681, C172, $D$2:$D$681, D172, $E$2:$E$681, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30221,11 +30221,11 @@
         <v>4120</v>
       </c>
       <c r="M173" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>270</v>
       </c>
       <c r="N173" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B173, $C$2:$C$681, C173, $D$2:$D$681, D173, $E$2:$E$681, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="39" t="s">
@@ -30271,11 +30271,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M174" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N174" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B174, $C$2:$C$681, C174, $D$2:$D$681, D174, $E$2:$E$681, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="39" t="s">
@@ -30321,11 +30321,11 @@
         <v>14552</v>
       </c>
       <c r="M175" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B175, $C$2:$C$681, C175, $D$2:$D$681, D175, $E$2:$E$681, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="38" t="s">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="J176" s="34"/>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B176, $C$2:$C$681, C176, $D$2:$D$681, D176, $E$2:$E$681, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
         <v>650</v>
       </c>
       <c r="N177" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B177, $C$2:$C$681, C177, $D$2:$D$681, D177, $E$2:$E$681, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P177" s="29"/>
@@ -30443,7 +30443,7 @@
       </c>
       <c r="J178" s="34"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B178, $C$2:$C$681, C178, $D$2:$D$681, D178, $E$2:$E$681, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
         <v>650</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B179, $C$2:$C$681, C179, $D$2:$D$681, D179, $E$2:$E$681, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="29"/>
@@ -30526,7 +30526,7 @@
         <v>116</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B180, $C$2:$C$681, C180, $D$2:$D$681, D180, $E$2:$E$681, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30572,7 +30572,7 @@
         <v>527.5</v>
       </c>
       <c r="N181" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B181, $C$2:$C$681, C181, $D$2:$D$681, D181, $E$2:$E$681, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="29"/>
@@ -30615,7 +30615,7 @@
       <c r="L182" s="27"/>
       <c r="M182" s="27"/>
       <c r="N182" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B182, $C$2:$C$681, C182, $D$2:$D$681, D182, $E$2:$E$681, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="29"/>
@@ -30663,7 +30663,7 @@
         <v>1400</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B183, $C$2:$C$681, C183, $D$2:$D$681, D183, $E$2:$E$681, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="38" t="s">
@@ -30705,7 +30705,7 @@
       <c r="L184" s="18"/>
       <c r="M184" s="18"/>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B184, $C$2:$C$681, C184, $D$2:$D$681, D184, $E$2:$E$681, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="10"/>
@@ -30753,7 +30753,7 @@
         <v>376</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B185, $C$2:$C$681, C185, $D$2:$D$681, D185, $E$2:$E$681, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30789,7 +30789,7 @@
         <v>192</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B186, $C$2:$C$681, C186, $D$2:$D$681, D186, $E$2:$E$681, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30823,7 +30823,7 @@
       </c>
       <c r="J187" s="34"/>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B187, $C$2:$C$681, C187, $D$2:$D$681, D187, $E$2:$E$681, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30869,7 +30869,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B188, $C$2:$C$681, C188, $D$2:$D$681, D188, $E$2:$E$681, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P188" s="25"/>
@@ -30906,7 +30906,7 @@
         <v>117</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B189, $C$2:$C$681, C189, $D$2:$D$681, D189, $E$2:$E$681, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30952,7 +30952,7 @@
         <v>250</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B190, $C$2:$C$681, C190, $D$2:$D$681, D190, $E$2:$E$681, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30998,7 +30998,7 @@
         <v>300</v>
       </c>
       <c r="N191" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B191, $C$2:$C$681, C191, $D$2:$D$681, D191, $E$2:$E$681, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31034,7 +31034,7 @@
         <v>117</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B192, $C$2:$C$681, C192, $D$2:$D$681, D192, $E$2:$E$681, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="29"/>
@@ -31081,7 +31081,7 @@
         <v>500</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B193, $C$2:$C$681, C193, $D$2:$D$681, D193, $E$2:$E$681, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="38" t="s">
@@ -31120,7 +31120,7 @@
         <v>116</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B194, $C$2:$C$681, C194, $D$2:$D$681, D194, $E$2:$E$681, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$681, B194, $C$2:$C$681, C194, $D$2:$D$681, D194, $E$2:$E$681, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -31156,7 +31156,7 @@
         <v>117</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B195, $C$2:$C$681, C195, $D$2:$D$681, D195, $E$2:$E$681, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="29"/>
@@ -31203,7 +31203,7 @@
         <v>250</v>
       </c>
       <c r="N196" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B196, $C$2:$C$681, C196, $D$2:$D$681, D196, $E$2:$E$681, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31249,7 +31249,7 @@
         <v>275</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B197, $C$2:$C$681, C197, $D$2:$D$681, D197, $E$2:$E$681, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
         <v>260</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B198, $C$2:$C$681, C198, $D$2:$D$681, D198, $E$2:$E$681, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31341,7 +31341,7 @@
         <v>320</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B199, $C$2:$C$681, C199, $D$2:$D$681, D199, $E$2:$E$681, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31387,7 +31387,7 @@
         <v>448</v>
       </c>
       <c r="N200" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B200, $C$2:$C$681, C200, $D$2:$D$681, D200, $E$2:$E$681, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31423,7 +31423,7 @@
         <v>117</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B201, $C$2:$C$681, C201, $D$2:$D$681, D201, $E$2:$E$681, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="38" t="s">
@@ -31462,7 +31462,7 @@
         <v>116</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B202, $C$2:$C$681, C202, $D$2:$D$681, D202, $E$2:$E$681, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31508,7 +31508,7 @@
         <v>420</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B203, $C$2:$C$681, C203, $D$2:$D$681, D203, $E$2:$E$681, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31544,7 +31544,7 @@
         <v>117</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B204, $C$2:$C$681, C204, $D$2:$D$681, D204, $E$2:$E$681, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31580,7 +31580,7 @@
         <v>117</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B205, $C$2:$C$681, C205, $D$2:$D$681, D205, $E$2:$E$681, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31622,11 +31622,11 @@
         <v>10814</v>
       </c>
       <c r="M206" s="18">
-        <f t="shared" ref="M206:M211" si="6">ABS((D206*E206)-L206)</f>
+        <f t="shared" ref="M206:M211" si="10">ABS((D206*E206)-L206)</f>
         <v>501</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B206, $C$2:$C$681, C206, $D$2:$D$681, D206, $E$2:$E$681, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="38" t="s">
@@ -31671,11 +31671,11 @@
         <v>17940</v>
       </c>
       <c r="M207" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>10680</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B207, $C$2:$C$681, C207, $D$2:$D$681, D207, $E$2:$E$681, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31717,11 +31717,11 @@
         <v>14100</v>
       </c>
       <c r="M208" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>500</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B208, $C$2:$C$681, C208, $D$2:$D$681, D208, $E$2:$E$681, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31763,11 +31763,11 @@
         <v>6105</v>
       </c>
       <c r="M209" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>150</v>
       </c>
       <c r="N209" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B209, $C$2:$C$681, C209, $D$2:$D$681, D209, $E$2:$E$681, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31809,11 +31809,11 @@
         <v>6005</v>
       </c>
       <c r="M210" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
       <c r="N210" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B210, $C$2:$C$681, C210, $D$2:$D$681, D210, $E$2:$E$681, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31855,11 +31855,11 @@
         <v>12510</v>
       </c>
       <c r="M211" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>290</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B211, $C$2:$C$681, C211, $D$2:$D$681, D211, $E$2:$E$681, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31895,7 +31895,7 @@
         <v>117</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B212, $C$2:$C$681, C212, $D$2:$D$681, D212, $E$2:$E$681, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31929,7 +31929,7 @@
       </c>
       <c r="J213" s="34"/>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B213, $C$2:$C$681, C213, $D$2:$D$681, D213, $E$2:$E$681, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31965,7 +31965,7 @@
         <v>117</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B214, $C$2:$C$681, C214, $D$2:$D$681, D214, $E$2:$E$681, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="29"/>
@@ -32012,7 +32012,7 @@
         <v>300</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B215, $C$2:$C$681, C215, $D$2:$D$681, D215, $E$2:$E$681, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32058,7 +32058,7 @@
         <v>300</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B216, $C$2:$C$681, C216, $D$2:$D$681, D216, $E$2:$E$681, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32104,7 +32104,7 @@
         <v>500</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B217, $C$2:$C$681, C217, $D$2:$D$681, D217, $E$2:$E$681, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32140,7 +32140,7 @@
         <v>54</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B218, $C$2:$C$681, C218, $D$2:$D$681, D218, $E$2:$E$681, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32174,7 +32174,7 @@
       </c>
       <c r="J219" s="34"/>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B219, $C$2:$C$681, C219, $D$2:$D$681, D219, $E$2:$E$681, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32213,7 +32213,7 @@
       <c r="L220" s="43"/>
       <c r="M220" s="43"/>
       <c r="N220" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B220, $C$2:$C$681, C220, $D$2:$D$681, D220, $E$2:$E$681, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O220" s="24"/>
@@ -32263,7 +32263,7 @@
         <v>300</v>
       </c>
       <c r="N221" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B221, $C$2:$C$681, C221, $D$2:$D$681, D221, $E$2:$E$681, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="29"/>
@@ -32311,7 +32311,7 @@
         <v>188</v>
       </c>
       <c r="N222" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B222, $C$2:$C$681, C222, $D$2:$D$681, D222, $E$2:$E$681, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32357,7 +32357,7 @@
         <v>10880</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B223, $C$2:$C$681, C223, $D$2:$D$681, D223, $E$2:$E$681, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="10"/>
@@ -32405,7 +32405,7 @@
         <v>300</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B224, $C$2:$C$681, C224, $D$2:$D$681, D224, $E$2:$E$681, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32451,7 +32451,7 @@
         <v>360</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B225, $C$2:$C$681, C225, $D$2:$D$681, D225, $E$2:$E$681, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32487,7 +32487,7 @@
         <v>116</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B226, $C$2:$C$681, C226, $D$2:$D$681, D226, $E$2:$E$681, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P226" s="29"/>
@@ -32534,7 +32534,7 @@
         <v>800</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B227, $C$2:$C$681, C227, $D$2:$D$681, D227, $E$2:$E$681, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="38" t="s">
@@ -32571,7 +32571,7 @@
       </c>
       <c r="J228" s="34"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B228, $C$2:$C$681, C228, $D$2:$D$681, D228, $E$2:$E$681, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32607,7 +32607,7 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B229, $C$2:$C$681, C229, $D$2:$D$681, D229, $E$2:$E$681, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32641,7 +32641,7 @@
       </c>
       <c r="J230" s="34"/>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B230, $C$2:$C$681, C230, $D$2:$D$681, D230, $E$2:$E$681, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32687,7 +32687,7 @@
         <v>500</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B231, $C$2:$C$681, C231, $D$2:$D$681, D231, $E$2:$E$681, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32723,7 +32723,7 @@
         <v>116</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B232, $C$2:$C$681, C232, $D$2:$D$681, D232, $E$2:$E$681, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32769,7 +32769,7 @@
         <v>816</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B233, $C$2:$C$681, C233, $D$2:$D$681, D233, $E$2:$E$681, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32805,7 +32805,7 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B234, $C$2:$C$681, C234, $D$2:$D$681, D234, $E$2:$E$681, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32842,7 +32842,7 @@
       <c r="L235" s="18"/>
       <c r="M235" s="18"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B235, $C$2:$C$681, C235, $D$2:$D$681, D235, $E$2:$E$681, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="10"/>
@@ -32878,7 +32878,7 @@
       </c>
       <c r="J236" s="34"/>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B236, $C$2:$C$681, C236, $D$2:$D$681, D236, $E$2:$E$681, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32912,7 +32912,7 @@
       </c>
       <c r="J237" s="34"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B237, $C$2:$C$681, C237, $D$2:$D$681, D237, $E$2:$E$681, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32946,7 +32946,7 @@
       </c>
       <c r="J238" s="34"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B238, $C$2:$C$681, C238, $D$2:$D$681, D238, $E$2:$E$681, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P238" s="29"/>
@@ -32993,7 +32993,7 @@
         <v>650</v>
       </c>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B239, $C$2:$C$681, C239, $D$2:$D$681, D239, $E$2:$E$681, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="10"/>
@@ -33030,7 +33030,7 @@
         <v>117</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B240, $C$2:$C$681, C240, $D$2:$D$681, D240, $E$2:$E$681, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33076,7 +33076,7 @@
         <v>651</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B241, $C$2:$C$681, C241, $D$2:$D$681, D241, $E$2:$E$681, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="J242" s="34"/>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B242, $C$2:$C$681, C242, $D$2:$D$681, D242, $E$2:$E$681, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33156,7 +33156,7 @@
         <v>400</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B243, $C$2:$C$681, C243, $D$2:$D$681, D243, $E$2:$E$681, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33193,7 +33193,7 @@
       <c r="L244" s="18"/>
       <c r="M244" s="18"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B244, $C$2:$C$681, C244, $D$2:$D$681, D244, $E$2:$E$681, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="10"/>
@@ -33241,7 +33241,7 @@
         <v>450</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B245, $C$2:$C$681, C245, $D$2:$D$681, D245, $E$2:$E$681, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -33279,7 +33279,7 @@
         <v>54</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B246, $C$2:$C$681, C246, $D$2:$D$681, D246, $E$2:$E$681, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="J247" s="34"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B247, $C$2:$C$681, C247, $D$2:$D$681, D247, $E$2:$E$681, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="29"/>
@@ -33360,7 +33360,7 @@
         <v>250</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B248, $C$2:$C$681, C248, $D$2:$D$681, D248, $E$2:$E$681, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O248" s="10"/>
@@ -33397,7 +33397,7 @@
         <v>116</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B249, $C$2:$C$681, C249, $D$2:$D$681, D249, $E$2:$E$681, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33431,7 +33431,7 @@
       </c>
       <c r="J250" s="34"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B250, $C$2:$C$681, C250, $D$2:$D$681, D250, $E$2:$E$681, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33468,7 +33468,7 @@
       <c r="L251" s="18"/>
       <c r="M251" s="18"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B251, $C$2:$C$681, C251, $D$2:$D$681, D251, $E$2:$E$681, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P251" s="10"/>
@@ -33515,7 +33515,7 @@
         <v>48320</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B252, $C$2:$C$681, C252, $D$2:$D$681, D252, $E$2:$E$681, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="38" t="s">
@@ -33565,7 +33565,7 @@
         <v>235</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B253, $C$2:$C$681, C253, $D$2:$D$681, D253, $E$2:$E$681, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33611,7 +33611,7 @@
         <v>370</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B254, $C$2:$C$681, C254, $D$2:$D$681, D254, $E$2:$E$681, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P254" s="29"/>
@@ -33651,7 +33651,7 @@
         <v>144</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B255, $C$2:$C$681, C255, $D$2:$D$681, D255, $E$2:$E$681, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33687,7 +33687,7 @@
         <v>116</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B256, $C$2:$C$681, C256, $D$2:$D$681, D256, $E$2:$E$681, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33723,7 +33723,7 @@
         <v>116</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B257, $C$2:$C$681, C257, $D$2:$D$681, D257, $E$2:$E$681, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33759,7 +33759,7 @@
         <v>116</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B258, $C$2:$C$681, C258, $D$2:$D$681, D258, $E$2:$E$681, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N307" si="11">IF(COUNTIFS( $B$2:$B$681, B258, $C$2:$C$681, C258, $D$2:$D$681, D258, $E$2:$E$681, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -33795,7 +33795,7 @@
         <v>116</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B259, $C$2:$C$681, C259, $D$2:$D$681, D259, $E$2:$E$681, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33837,11 +33837,11 @@
         <v>25800</v>
       </c>
       <c r="M260" s="18">
-        <f t="shared" ref="M260:M266" si="7">ABS((D260*E260)-L260)</f>
+        <f t="shared" ref="M260:M266" si="12">ABS((D260*E260)-L260)</f>
         <v>1800</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B260, $C$2:$C$681, C260, $D$2:$D$681, D260, $E$2:$E$681, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33883,11 +33883,11 @@
         <v>20260</v>
       </c>
       <c r="M261" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>480</v>
       </c>
       <c r="N261" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B261, $C$2:$C$681, C261, $D$2:$D$681, D261, $E$2:$E$681, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33929,11 +33929,11 @@
         <v>73800</v>
       </c>
       <c r="M262" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>47900</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B262, $C$2:$C$681, C262, $D$2:$D$681, D262, $E$2:$E$681, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="38" t="s">
@@ -33978,11 +33978,11 @@
         <v>15030</v>
       </c>
       <c r="M263" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>450</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B263, $C$2:$C$681, C263, $D$2:$D$681, D263, $E$2:$E$681, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34024,11 +34024,11 @@
         <v>25300</v>
       </c>
       <c r="M264" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>650</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B264, $C$2:$C$681, C264, $D$2:$D$681, D264, $E$2:$E$681, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="38" t="s">
@@ -34073,11 +34073,11 @@
         <v>12480</v>
       </c>
       <c r="M265" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>495</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B265, $C$2:$C$681, C265, $D$2:$D$681, D265, $E$2:$E$681, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="38" t="s">
@@ -34122,11 +34122,11 @@
         <v>13300</v>
       </c>
       <c r="M266" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B266, $C$2:$C$681, C266, $D$2:$D$681, D266, $E$2:$E$681, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34160,7 +34160,7 @@
       </c>
       <c r="J267" s="34"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B267, $C$2:$C$681, C267, $D$2:$D$681, D267, $E$2:$E$681, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34206,7 +34206,7 @@
         <v>300</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B268, $C$2:$C$681, C268, $D$2:$D$681, D268, $E$2:$E$681, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="38" t="s">
@@ -34249,7 +34249,7 @@
       <c r="L269" s="18"/>
       <c r="M269" s="18"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B269, $C$2:$C$681, C269, $D$2:$D$681, D269, $E$2:$E$681, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="10"/>
@@ -34297,7 +34297,7 @@
         <v>650</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B270, $C$2:$C$681, C270, $D$2:$D$681, D270, $E$2:$E$681, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O270"/>
@@ -34345,7 +34345,7 @@
         <v>260</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B271, $C$2:$C$681, C271, $D$2:$D$681, D271, $E$2:$E$681, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34381,7 +34381,7 @@
         <v>116</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B272, $C$2:$C$681, C272, $D$2:$D$681, D272, $E$2:$E$681, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34427,7 +34427,7 @@
         <v>47480</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B273, $C$2:$C$681, C273, $D$2:$D$681, D273, $E$2:$E$681, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34473,7 +34473,7 @@
         <v>340</v>
       </c>
       <c r="N274" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B274, $C$2:$C$681, C274, $D$2:$D$681, D274, $E$2:$E$681, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34519,7 +34519,7 @@
         <v>300</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B275, $C$2:$C$681, C275, $D$2:$D$681, D275, $E$2:$E$681, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="J276" s="34"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B276, $C$2:$C$681, C276, $D$2:$D$681, D276, $E$2:$E$681, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
         <v>300</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B277, $C$2:$C$681, C277, $D$2:$D$681, D277, $E$2:$E$681, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34635,7 +34635,7 @@
         <v>117</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B278, $C$2:$C$681, C278, $D$2:$D$681, D278, $E$2:$E$681, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34681,7 +34681,7 @@
         <v>300</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B279, $C$2:$C$681, C279, $D$2:$D$681, D279, $E$2:$E$681, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34727,7 +34727,7 @@
         <v>285</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B280, $C$2:$C$681, C280, $D$2:$D$681, D280, $E$2:$E$681, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34773,7 +34773,7 @@
         <v>726</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B281, $C$2:$C$681, C281, $D$2:$D$681, D281, $E$2:$E$681, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34819,7 +34819,7 @@
         <v>250</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B282, $C$2:$C$681, C282, $D$2:$D$681, D282, $E$2:$E$681, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34860,7 +34860,7 @@
       <c r="L283" s="17"/>
       <c r="M283" s="17"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B283, $C$2:$C$681, C283, $D$2:$D$681, D283, $E$2:$E$681, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
         <v>116</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B284, $C$2:$C$681, C284, $D$2:$D$681, D284, $E$2:$E$681, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="J285" s="34"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B285, $C$2:$C$681, C285, $D$2:$D$681, D285, $E$2:$E$681, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34966,7 +34966,7 @@
         <v>152</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B286, $C$2:$C$681, C286, $D$2:$D$681, D286, $E$2:$E$681, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35012,7 +35012,7 @@
         <v>275</v>
       </c>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B287, $C$2:$C$681, C287, $D$2:$D$681, D287, $E$2:$E$681, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35046,7 +35046,7 @@
       </c>
       <c r="J288" s="34"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B288, $C$2:$C$681, C288, $D$2:$D$681, D288, $E$2:$E$681, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35082,7 +35082,7 @@
         <v>116</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B289, $C$2:$C$681, C289, $D$2:$D$681, D289, $E$2:$E$681, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35128,7 +35128,7 @@
         <v>250</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B290, $C$2:$C$681, C290, $D$2:$D$681, D290, $E$2:$E$681, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35174,7 +35174,7 @@
         <v>250</v>
       </c>
       <c r="N291" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B291, $C$2:$C$681, C291, $D$2:$D$681, D291, $E$2:$E$681, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O291" s="10"/>
@@ -35209,7 +35209,7 @@
       </c>
       <c r="J292" s="34"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B292, $C$2:$C$681, C292, $D$2:$D$681, D292, $E$2:$E$681, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35246,7 +35246,7 @@
       <c r="L293" s="18"/>
       <c r="M293" s="18"/>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B293, $C$2:$C$681, C293, $D$2:$D$681, D293, $E$2:$E$681, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O293" s="10"/>
@@ -35294,7 +35294,7 @@
         <v>300</v>
       </c>
       <c r="N294" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B294, $C$2:$C$681, C294, $D$2:$D$681, D294, $E$2:$E$681, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35330,7 +35330,7 @@
         <v>54</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B295, $C$2:$C$681, C295, $D$2:$D$681, D295, $E$2:$E$681, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35366,7 +35366,7 @@
         <v>117</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B296, $C$2:$C$681, C296, $D$2:$D$681, D296, $E$2:$E$681, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35402,7 +35402,7 @@
         <v>117</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B297, $C$2:$C$681, C297, $D$2:$D$681, D297, $E$2:$E$681, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       <c r="L298" s="27"/>
       <c r="M298" s="27"/>
       <c r="N298" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B298, $C$2:$C$681, C298, $D$2:$D$681, D298, $E$2:$E$681, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O298" s="29"/>
@@ -35482,7 +35482,7 @@
       <c r="L299" s="27"/>
       <c r="M299" s="27"/>
       <c r="N299" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B299, $C$2:$C$681, C299, $D$2:$D$681, D299, $E$2:$E$681, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O299" s="29"/>
@@ -35520,7 +35520,7 @@
         <v>116</v>
       </c>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B300, $C$2:$C$681, C300, $D$2:$D$681, D300, $E$2:$E$681, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35558,7 +35558,7 @@
         <v>700</v>
       </c>
       <c r="N301" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B301, $C$2:$C$681, C301, $D$2:$D$681, D301, $E$2:$E$681, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35592,11 +35592,11 @@
         <v>9393.5</v>
       </c>
       <c r="M302" s="18">
-        <f t="shared" ref="M302:M307" si="8">ABS((D302*E302)-L302)</f>
+        <f t="shared" ref="M302:M307" si="13">ABS((D302*E302)-L302)</f>
         <v>656.5</v>
       </c>
       <c r="N302" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B302, $C$2:$C$681, C302, $D$2:$D$681, D302, $E$2:$E$681, E302) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35630,11 +35630,11 @@
         <v>17020</v>
       </c>
       <c r="M303" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>650</v>
       </c>
       <c r="N303" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B303, $C$2:$C$681, C303, $D$2:$D$681, D303, $E$2:$E$681, E303) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35668,11 +35668,11 @@
         <v>4110</v>
       </c>
       <c r="M304" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N304" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B304, $C$2:$C$681, C304, $D$2:$D$681, D304, $E$2:$E$681, E304) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35706,11 +35706,11 @@
         <v>19395</v>
       </c>
       <c r="M305" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>450</v>
       </c>
       <c r="N305" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B305, $C$2:$C$681, C305, $D$2:$D$681, D305, $E$2:$E$681, E305) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35744,11 +35744,11 @@
         <v>17487</v>
       </c>
       <c r="M306" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>400</v>
       </c>
       <c r="N306" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B306, $C$2:$C$681, C306, $D$2:$D$681, D306, $E$2:$E$681, E306) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35782,11 +35782,11 @@
         <v>8570</v>
       </c>
       <c r="M307" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>250</v>
       </c>
       <c r="N307" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$681, B307, $C$2:$C$681, C307, $D$2:$D$681, D307, $E$2:$E$681, E307) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
